--- a/DesignConfig.xlsx
+++ b/DesignConfig.xlsx
@@ -201,7 +201,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
@@ -371,6 +371,24 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -695,7 +713,7 @@
     <row r="1" ht="44.09999847412109" customHeight="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
-          <t>OneSatSim 全参数化设计配置表（单表整合版）</t>
+          <t>12UCubeSat 全参数化设计配置表（单表整合版）</t>
         </is>
       </c>
       <c r="B1" s="53" t="n"/>
@@ -840,7 +858,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>最终文件必须放在 OneSatSim 工程根目录，不再要求用户进入 tools/Input。</t>
+          <t>最终文件必须放在 12UCubeSat 工程根目录，不再要求用户进入 tools/Input。</t>
         </is>
       </c>
     </row>
@@ -969,10 +987,10 @@
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>2026-09-06T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
+          <t>2026-10-01T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>UTC</t>
         </is>
@@ -996,10 +1014,10 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>2026-09-07T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
+          <t>2026-10-02T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>UTC</t>
         </is>
@@ -1024,7 +1042,7 @@
       <c r="B7" s="19" t="n">
         <v>86400</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -1048,10 +1066,10 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>2026-09-06T00:00:00.000Z</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
+          <t>2026-10-01T00:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>UTC</t>
         </is>
@@ -1078,7 +1096,7 @@
           <t>Cartesian</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1105,7 +1123,7 @@
           <t>GCRS</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1132,7 +1150,7 @@
           <t>GCRS</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1155,9 +1173,9 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>-493801.2739989999</v>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
+        <v>-493801.2739989998</v>
+      </c>
+      <c r="C12" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -1182,7 +1200,7 @@
       <c r="B13" s="19" t="n">
         <v>-752595.4965559999</v>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -1205,9 +1223,9 @@
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>-6776165.492715</v>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
+        <v>-6776165.492714998</v>
+      </c>
+      <c r="C14" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -1232,7 +1250,7 @@
       <c r="B15" s="19" t="n">
         <v>-5490.252537677</v>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -1257,7 +1275,7 @@
       <c r="B16" s="22" t="n">
         <v>5304.349223451001</v>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="63" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -1282,7 +1300,7 @@
       <c r="B17" s="19" t="n">
         <v>-172.811574358</v>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -1305,9 +1323,9 @@
         </is>
       </c>
       <c r="B18" s="22" t="n">
-        <v>6835361.40000093</v>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
+        <v>6835361.400000924</v>
+      </c>
+      <c r="C18" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -1330,9 +1348,9 @@
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>0.002106700032946816</v>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
+        <v>0.002106700032946844</v>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1357,7 +1375,7 @@
       <c r="B20" s="22" t="n">
         <v>1.700500174166025</v>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C20" s="63" t="inlineStr">
         <is>
           <t>rad</t>
         </is>
@@ -1384,7 +1402,7 @@
           <t>2396752.5 .. 2506352.5</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="62" t="inlineStr">
         <is>
           <t>TDB</t>
         </is>
@@ -1411,7 +1429,7 @@
           <t>41684.0 .. 61659.0</t>
         </is>
       </c>
-      <c r="C22" s="25" t="inlineStr">
+      <c r="C22" s="63" t="inlineStr">
         <is>
           <t>UTC MJD</t>
         </is>
@@ -1438,7 +1456,7 @@
           <t>PREDICTED</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -1465,7 +1483,7 @@
           <t>c1c7feeab882263fc493a9d5a5b2ddd71b54826cdf65d8d17a76126b260a49f2</t>
         </is>
       </c>
-      <c r="C24" s="25" t="inlineStr">
+      <c r="C24" s="63" t="inlineStr">
         <is>
           <t>SHA-256</t>
         </is>
@@ -1492,7 +1510,7 @@
           <t>80119694522717471744a78b28bc872e998523f8b1e2007424f9cd08af7ac4c6</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="62" t="inlineStr">
         <is>
           <t>SHA-256</t>
         </is>
@@ -1519,7 +1537,7 @@
           <t>6cb6f5d4b819f2e568e25db4b0b26d89dedf031fdffb18bc94d40f4e94e268d7</t>
         </is>
       </c>
-      <c r="C26" s="25" t="inlineStr">
+      <c r="C26" s="63" t="inlineStr">
         <is>
           <t>SHA-256</t>
         </is>
@@ -1543,10 +1561,10 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>7d6372e7d8e2c950c9e6ea8c5adc0a2b1b490944fecdb272d92b4517236d0c83</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
+          <t>52c098772698e2ca0ce8ce99ae68e33d725dcec5fa9d0c52b64e02cf9502533b</t>
+        </is>
+      </c>
+      <c r="C27" s="62" t="inlineStr">
         <is>
           <t>SHA-256</t>
         </is>
@@ -1571,7 +1589,7 @@
       <c r="B28" s="22" t="n">
         <v>2.5</v>
       </c>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="C28" s="63" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -1594,9 +1612,9 @@
         </is>
       </c>
       <c r="B29" s="19" t="n">
-        <v>0.007273582983030732</v>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
+        <v>0.007274395899786768</v>
+      </c>
+      <c r="C29" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -1619,9 +1637,9 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>0.009260415667292063</v>
-      </c>
-      <c r="C30" s="25" t="inlineStr">
+        <v>0.009261920757415854</v>
+      </c>
+      <c r="C30" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -1644,9 +1662,9 @@
         </is>
       </c>
       <c r="B31" s="19" t="n">
-        <v>0.01996494850462639</v>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
+        <v>0.01996494216246775</v>
+      </c>
+      <c r="C31" s="62" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -1715,7 +1733,7 @@
     <row r="1" ht="44.09999847412109" customHeight="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
-          <t>OneSatSim · 配置元数据</t>
+          <t>12UCubeSat · 配置元数据</t>
         </is>
       </c>
       <c r="B1" s="53" t="n"/>
@@ -1784,12 +1802,12 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>OneSatSim_DefaultDesign</t>
+          <t>MOSAIC_12UCubeSat_DefaultDesign</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>OneSatSim_DefaultDesign</t>
+          <t>MOSAIC_12UCubeSat_DefaultDesign</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -1984,7 +2002,7 @@
       <c r="B5" s="21" t="n">
         <v>6835.3614</v>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>km</t>
         </is>
@@ -2020,7 +2038,7 @@
       <c r="B6" s="21" t="n">
         <v>0.002106700032949448</v>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -2056,7 +2074,7 @@
       <c r="B7" s="21" t="n">
         <v>97.43148304096999</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
@@ -2092,7 +2110,7 @@
       <c r="B8" s="21" t="n">
         <v>135.81746770934</v>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
@@ -2128,7 +2146,7 @@
       <c r="B9" s="21" t="n">
         <v>268.81290697642</v>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
@@ -2164,7 +2182,7 @@
       <c r="B10" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
@@ -2200,7 +2218,7 @@
       <c r="B11" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -2238,7 +2256,7 @@
           <t>Cartesian</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="63" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2278,7 +2296,7 @@
           <t>GCRS</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -2314,7 +2332,7 @@
         </is>
       </c>
       <c r="B14" s="56" t="n"/>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="63" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
@@ -2348,7 +2366,7 @@
       <c r="B15" s="21" t="n">
         <v>-493801.273999</v>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -2384,7 +2402,7 @@
       <c r="B16" s="21" t="n">
         <v>-752595.496556</v>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -2420,7 +2438,7 @@
       <c r="B17" s="21" t="n">
         <v>-6776165.492715</v>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -2456,7 +2474,7 @@
       <c r="B18" s="21" t="n">
         <v>-5490.252537677</v>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="63" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -2492,7 +2510,7 @@
       <c r="B19" s="21" t="n">
         <v>5304.349223451</v>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
@@ -2708,10 +2726,10 @@
       <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18" t="n">
+      <c r="B5" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="62" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -2731,7 +2749,7 @@
       <c r="H5" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="62" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="19" t="inlineStr">
@@ -2749,10 +2767,10 @@
       <c r="A6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="25" t="n">
+      <c r="B6" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="63" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -2772,7 +2790,7 @@
       <c r="H6" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="63" t="n">
         <v>2</v>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -2790,10 +2808,10 @@
       <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18" t="n">
+      <c r="B7" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="62" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -2813,7 +2831,7 @@
       <c r="H7" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="62" t="n">
         <v>3</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -2831,10 +2849,10 @@
       <c r="A8" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="25" t="b">
+      <c r="B8" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="63" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -2854,7 +2872,7 @@
       <c r="H8" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="I8" s="25" t="n">
+      <c r="I8" s="63" t="n">
         <v>4</v>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -2872,10 +2890,10 @@
       <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="b">
+      <c r="B9" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="62" t="n">
         <v>5</v>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -2895,7 +2913,7 @@
       <c r="H9" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="62" t="n">
         <v>5</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
@@ -2913,10 +2931,10 @@
       <c r="A10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" s="25" t="n">
+      <c r="B10" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="63" t="n">
         <v>6</v>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -2936,7 +2954,7 @@
       <c r="H10" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="I10" s="25" t="n">
+      <c r="I10" s="63" t="n">
         <v>6</v>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -2954,10 +2972,10 @@
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="b">
+      <c r="B11" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="62" t="n">
         <v>7</v>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -2977,7 +2995,7 @@
       <c r="H11" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="62" t="n">
         <v>7</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
@@ -3171,10 +3189,10 @@
       <c r="A5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" s="18" t="n">
+      <c r="B5" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="62" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="19" t="inlineStr">
@@ -3194,7 +3212,7 @@
       <c r="H5" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="62" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="19" t="inlineStr">
@@ -3212,10 +3230,10 @@
       <c r="A6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="25" t="n">
+      <c r="B6" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="63" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -3235,7 +3253,7 @@
       <c r="H6" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="63" t="n">
         <v>1</v>
       </c>
       <c r="J6" s="22" t="inlineStr">
@@ -3253,10 +3271,10 @@
       <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18" t="n">
+      <c r="B7" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="62" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="19" t="inlineStr">
@@ -3276,7 +3294,7 @@
       <c r="H7" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="I7" s="62" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -3294,10 +3312,10 @@
       <c r="A8" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" s="25" t="n">
+      <c r="B8" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="63" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -3317,7 +3335,7 @@
       <c r="H8" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I8" s="25" t="n">
+      <c r="I8" s="63" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="22" t="inlineStr">
@@ -3335,10 +3353,10 @@
       <c r="A9" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" s="18" t="n">
+      <c r="B9" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="62" t="n">
         <v>5</v>
       </c>
       <c r="D9" s="19" t="inlineStr">
@@ -3358,7 +3376,7 @@
       <c r="H9" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="I9" s="62" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="19" t="inlineStr">
@@ -3376,10 +3394,10 @@
       <c r="A10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" s="25" t="n">
+      <c r="B10" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="63" t="n">
         <v>6</v>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -3399,7 +3417,7 @@
       <c r="H10" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I10" s="25" t="n">
+      <c r="I10" s="63" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="22" t="inlineStr">
@@ -3417,10 +3435,10 @@
       <c r="A11" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" s="18" t="n">
+      <c r="B11" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" s="62" t="n">
         <v>7</v>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -3440,7 +3458,7 @@
       <c r="H11" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="I11" s="62" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="19" t="inlineStr">
@@ -3458,10 +3476,10 @@
       <c r="A12" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="25" t="n">
+      <c r="B12" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="63" t="n">
         <v>8</v>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -3481,7 +3499,7 @@
       <c r="H12" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I12" s="25" t="n">
+      <c r="I12" s="63" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="22" t="inlineStr">
@@ -3499,10 +3517,10 @@
       <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="18" t="b">
-        <v>1</v>
-      </c>
-      <c r="C13" s="18" t="n">
+      <c r="B13" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" s="62" t="n">
         <v>9</v>
       </c>
       <c r="D13" s="19" t="inlineStr">
@@ -3522,7 +3540,7 @@
       <c r="H13" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="62" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="19" t="inlineStr">
@@ -3540,10 +3558,10 @@
       <c r="A14" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="25" t="b">
-        <v>1</v>
-      </c>
-      <c r="C14" s="25" t="n">
+      <c r="B14" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="63" t="n">
         <v>10</v>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -3563,7 +3581,7 @@
       <c r="H14" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I14" s="25" t="n">
+      <c r="I14" s="63" t="n">
         <v>1</v>
       </c>
       <c r="J14" s="22" t="inlineStr">
@@ -3581,10 +3599,10 @@
       <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15" s="18" t="n">
+      <c r="B15" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="62" t="n">
         <v>11</v>
       </c>
       <c r="D15" s="19" t="inlineStr">
@@ -3604,7 +3622,7 @@
       <c r="H15" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I15" s="18" t="n">
+      <c r="I15" s="62" t="n">
         <v>18</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
@@ -3622,10 +3640,10 @@
       <c r="A16" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="25" t="b">
+      <c r="B16" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="63" t="n">
         <v>12</v>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -3645,7 +3663,7 @@
       <c r="H16" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I16" s="25" t="n">
+      <c r="I16" s="63" t="n">
         <v>17</v>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -3663,10 +3681,10 @@
       <c r="A17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="18" t="b">
+      <c r="B17" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="62" t="n">
         <v>13</v>
       </c>
       <c r="D17" s="19" t="inlineStr">
@@ -3686,7 +3704,7 @@
       <c r="H17" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I17" s="18" t="n">
+      <c r="I17" s="62" t="n">
         <v>16</v>
       </c>
       <c r="J17" s="19" t="inlineStr">
@@ -3704,10 +3722,10 @@
       <c r="A18" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="25" t="b">
+      <c r="B18" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="63" t="n">
         <v>14</v>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -3727,7 +3745,7 @@
       <c r="H18" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="63" t="n">
         <v>15</v>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -3745,10 +3763,10 @@
       <c r="A19" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="18" t="b">
+      <c r="B19" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C19" s="18" t="n">
+      <c r="C19" s="62" t="n">
         <v>15</v>
       </c>
       <c r="D19" s="19" t="inlineStr">
@@ -3768,7 +3786,7 @@
       <c r="H19" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I19" s="18" t="n">
+      <c r="I19" s="62" t="n">
         <v>14</v>
       </c>
       <c r="J19" s="19" t="inlineStr">
@@ -3786,10 +3804,10 @@
       <c r="A20" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="25" t="b">
+      <c r="B20" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C20" s="25" t="n">
+      <c r="C20" s="63" t="n">
         <v>16</v>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -3809,7 +3827,7 @@
       <c r="H20" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="63" t="n">
         <v>13</v>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -3827,10 +3845,10 @@
       <c r="A21" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C21" s="18" t="n">
+      <c r="B21" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C21" s="62" t="n">
         <v>17</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
@@ -3850,7 +3868,7 @@
       <c r="H21" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I21" s="18" t="n">
+      <c r="I21" s="62" t="n">
         <v>12</v>
       </c>
       <c r="J21" s="19" t="inlineStr">
@@ -3868,10 +3886,10 @@
       <c r="A22" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="25" t="b">
+      <c r="B22" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C22" s="25" t="n">
+      <c r="C22" s="63" t="n">
         <v>18</v>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -3891,7 +3909,7 @@
       <c r="H22" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I22" s="25" t="n">
+      <c r="I22" s="63" t="n">
         <v>11</v>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -3909,10 +3927,10 @@
       <c r="A23" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="18" t="b">
-        <v>0</v>
-      </c>
-      <c r="C23" s="18" t="n">
+      <c r="B23" s="62" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23" s="62" t="n">
         <v>19</v>
       </c>
       <c r="D23" s="19" t="inlineStr">
@@ -3932,7 +3950,7 @@
       <c r="H23" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I23" s="18" t="n">
+      <c r="I23" s="62" t="n">
         <v>10</v>
       </c>
       <c r="J23" s="19" t="inlineStr">
@@ -3950,10 +3968,10 @@
       <c r="A24" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="25" t="b">
+      <c r="B24" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="63" t="n">
         <v>20</v>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -3973,7 +3991,7 @@
       <c r="H24" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I24" s="25" t="n">
+      <c r="I24" s="63" t="n">
         <v>9</v>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -3991,10 +4009,10 @@
       <c r="A25" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="18" t="b">
+      <c r="B25" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C25" s="18" t="n">
+      <c r="C25" s="62" t="n">
         <v>21</v>
       </c>
       <c r="D25" s="19" t="inlineStr">
@@ -4014,7 +4032,7 @@
       <c r="H25" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I25" s="18" t="n">
+      <c r="I25" s="62" t="n">
         <v>8</v>
       </c>
       <c r="J25" s="19" t="inlineStr">
@@ -4032,10 +4050,10 @@
       <c r="A26" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="25" t="b">
-        <v>0</v>
-      </c>
-      <c r="C26" s="25" t="n">
+      <c r="B26" s="63" t="b">
+        <v>1</v>
+      </c>
+      <c r="C26" s="63" t="n">
         <v>22</v>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -4055,7 +4073,7 @@
       <c r="H26" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I26" s="25" t="n">
+      <c r="I26" s="63" t="n">
         <v>7</v>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -4073,10 +4091,10 @@
       <c r="A27" s="10" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="b">
+      <c r="B27" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C27" s="18" t="n">
+      <c r="C27" s="62" t="n">
         <v>23</v>
       </c>
       <c r="D27" s="19" t="inlineStr">
@@ -4096,7 +4114,7 @@
       <c r="H27" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I27" s="18" t="n">
+      <c r="I27" s="62" t="n">
         <v>6</v>
       </c>
       <c r="J27" s="19" t="inlineStr">
@@ -4114,10 +4132,10 @@
       <c r="A28" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="25" t="b">
+      <c r="B28" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="63" t="n">
         <v>24</v>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -4137,7 +4155,7 @@
       <c r="H28" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I28" s="25" t="n">
+      <c r="I28" s="63" t="n">
         <v>5</v>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -4155,10 +4173,10 @@
       <c r="A29" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="18" t="b">
+      <c r="B29" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C29" s="18" t="n">
+      <c r="C29" s="62" t="n">
         <v>25</v>
       </c>
       <c r="D29" s="19" t="inlineStr">
@@ -4178,7 +4196,7 @@
       <c r="H29" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="18" t="n">
+      <c r="I29" s="62" t="n">
         <v>4</v>
       </c>
       <c r="J29" s="19" t="inlineStr">
@@ -4196,10 +4214,10 @@
       <c r="A30" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="25" t="b">
+      <c r="B30" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="63" t="n">
         <v>26</v>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -4219,7 +4237,7 @@
       <c r="H30" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I30" s="25" t="n">
+      <c r="I30" s="63" t="n">
         <v>3</v>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -4237,10 +4255,10 @@
       <c r="A31" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="18" t="b">
+      <c r="B31" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C31" s="18" t="n">
+      <c r="C31" s="62" t="n">
         <v>27</v>
       </c>
       <c r="D31" s="19" t="inlineStr">
@@ -4260,7 +4278,7 @@
       <c r="H31" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I31" s="62" t="n">
         <v>2</v>
       </c>
       <c r="J31" s="19" t="inlineStr">
@@ -4278,10 +4296,10 @@
       <c r="A32" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="25" t="b">
+      <c r="B32" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="63" t="n">
         <v>28</v>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -4301,7 +4319,7 @@
       <c r="H32" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I32" s="25" t="n">
+      <c r="I32" s="63" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -4319,10 +4337,10 @@
       <c r="A33" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="18" t="b">
+      <c r="B33" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="62" t="n"/>
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
       <c r="F33" s="19" t="n"/>
@@ -4330,7 +4348,7 @@
       <c r="H33" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I33" s="18" t="n"/>
+      <c r="I33" s="62" t="n"/>
       <c r="J33" s="19" t="inlineStr">
         <is>
           <t>Scenarios.ScenarioConfig.imagingTargets[29]</t>
@@ -4346,10 +4364,10 @@
       <c r="A34" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="25" t="b">
+      <c r="B34" s="63" t="b">
         <v>0</v>
       </c>
-      <c r="C34" s="25" t="n"/>
+      <c r="C34" s="63" t="n"/>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="22" t="n"/>
       <c r="F34" s="22" t="n"/>
@@ -4357,7 +4375,7 @@
       <c r="H34" s="22" t="n">
         <v>25</v>
       </c>
-      <c r="I34" s="25" t="n"/>
+      <c r="I34" s="63" t="n"/>
       <c r="J34" s="22" t="inlineStr">
         <is>
           <t>Scenarios.ScenarioConfig.imagingTargets[30]</t>
@@ -4373,10 +4391,10 @@
       <c r="A35" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="18" t="b">
+      <c r="B35" s="62" t="b">
         <v>0</v>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="62" t="n"/>
       <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="n"/>
       <c r="F35" s="19" t="n"/>
@@ -4384,7 +4402,7 @@
       <c r="H35" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I35" s="18" t="n"/>
+      <c r="I35" s="62" t="n"/>
       <c r="J35" s="19" t="inlineStr">
         <is>
           <t>Scenarios.ScenarioConfig.imagingTargets[31]</t>
@@ -4558,7 +4576,7 @@
       <c r="C5" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -4640,7 +4658,7 @@
       <c r="C7" s="21" t="n">
         <v>21.69859925096</v>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
@@ -4681,7 +4699,7 @@
       <c r="C8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>deg</t>
         </is>
@@ -4722,7 +4740,7 @@
       <c r="C9" s="21" t="n">
         <v>-0.00191946591</v>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t>deg/s</t>
         </is>
@@ -4763,7 +4781,7 @@
       <c r="C10" s="21" t="n">
         <v>-0.00418253461</v>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>deg/s</t>
         </is>
@@ -4804,7 +4822,7 @@
       <c r="C11" s="21" t="n">
         <v>-0.00095947512</v>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>deg/s</t>
         </is>
@@ -4927,7 +4945,7 @@
       <c r="C14" s="21" t="n">
         <v>6.11</v>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="63" t="inlineStr">
         <is>
           <t>degC</t>
         </is>
@@ -5009,7 +5027,7 @@
       <c r="C16" s="21" t="n">
         <v>3.79</v>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="63" t="inlineStr">
         <is>
           <t>degC</t>
         </is>
@@ -5091,7 +5109,7 @@
       <c r="C18" s="21" t="n">
         <v>-7.01</v>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="63" t="inlineStr">
         <is>
           <t>degC</t>
         </is>
@@ -5214,7 +5232,7 @@
       <c r="C21" s="21" t="n">
         <v>2.66</v>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="62" t="inlineStr">
         <is>
           <t>degC</t>
         </is>
@@ -5337,7 +5355,7 @@
       <c r="C24" s="21" t="n">
         <v>153.8</v>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="63" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
@@ -5378,7 +5396,7 @@
       <c r="C25" s="21" t="n">
         <v>-161.6</v>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="62" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
@@ -5563,7 +5581,7 @@
       <c r="B5" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -5596,7 +5614,7 @@
       <c r="B6" s="21" t="n">
         <v>86400</v>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -5629,7 +5647,7 @@
       <c r="B7" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -5660,9 +5678,9 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
+        <v>1e-07</v>
+      </c>
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5697,7 +5715,7 @@
           <t>ida</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5734,7 +5752,7 @@
           <t>spgmr</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5771,7 +5789,7 @@
           <t>coloredNumerical</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5806,7 +5824,7 @@
       <c r="B12" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5837,9 +5855,9 @@
         </is>
       </c>
       <c r="B13" s="56" t="n">
-        <v>46271</v>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
+        <v>46296</v>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
@@ -5874,7 +5892,7 @@
           <t>UTC</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C14" s="63" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -5978,7 +5996,7 @@
     <row r="1" ht="44.09999847412109" customHeight="1">
       <c r="A1" s="52" t="inlineStr">
         <is>
-          <t>OneSatSim · 八分系统组件设计参数（统一配置表）</t>
+          <t>12UCubeSat · 八分系统组件设计参数（统一配置表）</t>
         </is>
       </c>
       <c r="B1" s="53" t="n"/>
@@ -6135,7 +6153,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -6153,7 +6171,7 @@
       <c r="G5" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6211,7 +6229,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -6229,7 +6247,7 @@
       <c r="G6" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="25" t="inlineStr">
+      <c r="H6" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6287,7 +6305,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D7" s="18" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -6305,7 +6323,7 @@
       <c r="G7" s="21" t="n">
         <v>8.5</v>
       </c>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="H7" s="62" t="inlineStr">
         <is>
           <t>Ah</t>
         </is>
@@ -6363,7 +6381,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -6381,7 +6399,7 @@
       <c r="G8" s="21" t="n">
         <v>4.2</v>
       </c>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="H8" s="63" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -6435,7 +6453,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="D9" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -6453,7 +6471,7 @@
       <c r="G9" s="21" t="n">
         <v>3.2</v>
       </c>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="H9" s="62" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -6507,7 +6525,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D10" s="25" t="inlineStr">
+      <c r="D10" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -6525,7 +6543,7 @@
       <c r="G10" s="21" t="n">
         <v>0.018</v>
       </c>
-      <c r="H10" s="25" t="inlineStr">
+      <c r="H10" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -6579,7 +6597,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -6597,7 +6615,7 @@
       <c r="G11" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="H11" s="18" t="inlineStr">
+      <c r="H11" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6655,7 +6673,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D12" s="25" t="inlineStr">
+      <c r="D12" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -6673,7 +6691,7 @@
       <c r="G12" s="21" t="n">
         <v>0.98</v>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="H12" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6731,7 +6749,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="62" t="inlineStr">
         <is>
           <t>Life</t>
         </is>
@@ -6749,7 +6767,7 @@
       <c r="G13" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6807,7 +6825,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D14" s="63" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
@@ -6825,7 +6843,7 @@
       <c r="G14" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="H14" s="63" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -6879,7 +6897,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -6897,7 +6915,7 @@
       <c r="G15" s="21" t="n">
         <v>0.012</v>
       </c>
-      <c r="H15" s="18" t="inlineStr">
+      <c r="H15" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -6951,7 +6969,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -6969,7 +6987,7 @@
       <c r="G16" s="21" t="n">
         <v>110</v>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="H16" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -7027,7 +7045,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -7045,7 +7063,7 @@
       <c r="G17" s="21" t="n">
         <v>3200</v>
       </c>
-      <c r="H17" s="18" t="inlineStr">
+      <c r="H17" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -7099,7 +7117,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -7117,7 +7135,7 @@
       <c r="G18" s="21" t="n">
         <v>700</v>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="H18" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -7171,7 +7189,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -7189,7 +7207,7 @@
       <c r="G19" s="21" t="n">
         <v>0.65</v>
       </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="H19" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -7243,7 +7261,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D20" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -7261,7 +7279,7 @@
       <c r="G20" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H20" s="25" t="inlineStr">
+      <c r="H20" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -7315,7 +7333,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7333,7 +7351,7 @@
       <c r="G21" s="21" t="n">
         <v>2.35</v>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H21" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -7391,7 +7409,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D22" s="25" t="inlineStr">
+      <c r="D22" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7409,7 +7427,7 @@
       <c r="G22" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="25" t="inlineStr">
+      <c r="H22" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -7467,7 +7485,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7485,7 +7503,7 @@
       <c r="G23" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="18" t="inlineStr">
+      <c r="H23" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -7543,7 +7561,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7561,7 +7579,7 @@
       <c r="G24" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="25" t="inlineStr">
+      <c r="H24" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -7619,7 +7637,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D25" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7637,7 +7655,7 @@
       <c r="G25" s="21" t="n">
         <v>0.018</v>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="H25" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -7695,7 +7713,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D26" s="25" t="inlineStr">
+      <c r="D26" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7713,7 +7731,7 @@
       <c r="G26" s="21" t="n">
         <v>0.011</v>
       </c>
-      <c r="H26" s="25" t="inlineStr">
+      <c r="H26" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -7771,7 +7789,7 @@
           <t>Components.BatteryUnit</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="D27" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -7789,7 +7807,7 @@
       <c r="G27" s="21" t="n">
         <v>0.016</v>
       </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="H27" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -7847,7 +7865,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -7865,7 +7883,7 @@
       <c r="G28" s="21" t="n">
         <v>0.069156</v>
       </c>
-      <c r="H28" s="25" t="inlineStr">
+      <c r="H28" s="63" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -7923,7 +7941,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D29" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -7941,7 +7959,7 @@
       <c r="G29" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="H29" s="18" t="inlineStr">
+      <c r="H29" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -7999,7 +8017,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="63" t="inlineStr">
         <is>
           <t>Life</t>
         </is>
@@ -8017,7 +8035,7 @@
       <c r="G30" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H30" s="25" t="inlineStr">
+      <c r="H30" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8075,7 +8093,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="D31" s="62" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
@@ -8093,7 +8111,7 @@
       <c r="G31" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="18" t="inlineStr">
+      <c r="H31" s="62" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -8147,7 +8165,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D32" s="25" t="inlineStr">
+      <c r="D32" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -8165,7 +8183,7 @@
       <c r="G32" s="21" t="n">
         <v>0.965</v>
       </c>
-      <c r="H32" s="25" t="inlineStr">
+      <c r="H32" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8223,7 +8241,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="D33" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -8241,7 +8259,7 @@
       <c r="G33" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="H33" s="18" t="inlineStr">
+      <c r="H33" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8299,7 +8317,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D34" s="25" t="inlineStr">
+      <c r="D34" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -8317,7 +8335,7 @@
       <c r="G34" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H34" s="25" t="inlineStr">
+      <c r="H34" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8375,7 +8393,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D35" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -8393,7 +8411,7 @@
       <c r="G35" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="H35" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8451,7 +8469,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D36" s="25" t="inlineStr">
+      <c r="D36" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -8469,7 +8487,7 @@
       <c r="G36" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="H36" s="25" t="inlineStr">
+      <c r="H36" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -8523,7 +8541,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -8541,7 +8559,7 @@
       <c r="G37" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="H37" s="18" t="inlineStr">
+      <c r="H37" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -8595,7 +8613,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D38" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -8613,7 +8631,7 @@
       <c r="G38" s="21" t="n">
         <v>510</v>
       </c>
-      <c r="H38" s="25" t="inlineStr">
+      <c r="H38" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -8667,7 +8685,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -8685,7 +8703,7 @@
       <c r="G39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="H39" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8743,7 +8761,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D40" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -8761,7 +8779,7 @@
       <c r="G40" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H40" s="25" t="inlineStr">
+      <c r="H40" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8819,7 +8837,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="D41" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -8837,7 +8855,7 @@
       <c r="G41" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="18" t="inlineStr">
+      <c r="H41" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -8895,7 +8913,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D42" s="25" t="inlineStr">
+      <c r="D42" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -8913,7 +8931,7 @@
       <c r="G42" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="H42" s="25" t="inlineStr">
+      <c r="H42" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -8971,7 +8989,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -8989,7 +9007,7 @@
       <c r="G43" s="21" t="n">
         <v>0.113</v>
       </c>
-      <c r="H43" s="18" t="inlineStr">
+      <c r="H43" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -9047,7 +9065,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D44" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -9065,7 +9083,7 @@
       <c r="G44" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="25" t="inlineStr">
+      <c r="H44" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -9123,7 +9141,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="D45" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -9141,7 +9159,7 @@
       <c r="G45" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="18" t="inlineStr">
+      <c r="H45" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -9199,7 +9217,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D46" s="25" t="inlineStr">
+      <c r="D46" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -9217,7 +9235,7 @@
       <c r="G46" s="21" t="n">
         <v>0.003889</v>
       </c>
-      <c r="H46" s="25" t="inlineStr">
+      <c r="H46" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -9275,7 +9293,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D47" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -9293,7 +9311,7 @@
       <c r="G47" s="21" t="n">
         <v>0.002697</v>
       </c>
-      <c r="H47" s="18" t="inlineStr">
+      <c r="H47" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -9351,7 +9369,7 @@
           <t>Components.BodyMountedSolarArrayPlusXUnit</t>
         </is>
       </c>
-      <c r="D48" s="25" t="inlineStr">
+      <c r="D48" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -9369,7 +9387,7 @@
       <c r="G48" s="21" t="n">
         <v>0.001192</v>
       </c>
-      <c r="H48" s="25" t="inlineStr">
+      <c r="H48" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -9427,7 +9445,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="D49" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -9445,7 +9463,7 @@
       <c r="G49" s="21" t="n">
         <v>0.069156</v>
       </c>
-      <c r="H49" s="18" t="inlineStr">
+      <c r="H49" s="62" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -9503,7 +9521,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D50" s="25" t="inlineStr">
+      <c r="D50" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -9521,7 +9539,7 @@
       <c r="G50" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="H50" s="25" t="inlineStr">
+      <c r="H50" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9579,7 +9597,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="D51" s="62" t="inlineStr">
         <is>
           <t>Life</t>
         </is>
@@ -9597,7 +9615,7 @@
       <c r="G51" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="H51" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9655,7 +9673,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D52" s="25" t="inlineStr">
+      <c r="D52" s="63" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
@@ -9673,7 +9691,7 @@
       <c r="G52" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="H52" s="25" t="inlineStr">
+      <c r="H52" s="63" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -9727,7 +9745,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D53" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -9745,7 +9763,7 @@
       <c r="G53" s="21" t="n">
         <v>0.95</v>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="H53" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9803,7 +9821,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D54" s="25" t="inlineStr">
+      <c r="D54" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -9821,7 +9839,7 @@
       <c r="G54" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="H54" s="25" t="inlineStr">
+      <c r="H54" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9879,7 +9897,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D55" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -9897,7 +9915,7 @@
       <c r="G55" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="H55" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -9955,7 +9973,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D56" s="25" t="inlineStr">
+      <c r="D56" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -9973,7 +9991,7 @@
       <c r="G56" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H56" s="25" t="inlineStr">
+      <c r="H56" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10031,7 +10049,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D57" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -10049,7 +10067,7 @@
       <c r="G57" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="H57" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -10103,7 +10121,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D58" s="25" t="inlineStr">
+      <c r="D58" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -10121,7 +10139,7 @@
       <c r="G58" s="21" t="n">
         <v>0.04235</v>
       </c>
-      <c r="H58" s="25" t="inlineStr">
+      <c r="H58" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -10175,7 +10193,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -10193,7 +10211,7 @@
       <c r="G59" s="21" t="n">
         <v>525</v>
       </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="H59" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -10247,7 +10265,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D60" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10265,7 +10283,7 @@
       <c r="G60" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="25" t="inlineStr">
+      <c r="H60" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10323,7 +10341,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="D61" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10341,7 +10359,7 @@
       <c r="G61" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="18" t="inlineStr">
+      <c r="H61" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10399,7 +10417,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D62" s="25" t="inlineStr">
+      <c r="D62" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10417,7 +10435,7 @@
       <c r="G62" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H62" s="25" t="inlineStr">
+      <c r="H62" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -10475,7 +10493,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="D63" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10493,7 +10511,7 @@
       <c r="G63" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="H63" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -10551,7 +10569,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D64" s="25" t="inlineStr">
+      <c r="D64" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10569,7 +10587,7 @@
       <c r="G64" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H64" s="25" t="inlineStr">
+      <c r="H64" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -10627,7 +10645,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D65" s="18" t="inlineStr">
+      <c r="D65" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10645,7 +10663,7 @@
       <c r="G65" s="21" t="n">
         <v>0.113</v>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="H65" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -10703,7 +10721,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D66" s="25" t="inlineStr">
+      <c r="D66" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10721,7 +10739,7 @@
       <c r="G66" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H66" s="25" t="inlineStr">
+      <c r="H66" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -10779,7 +10797,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="D67" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10797,7 +10815,7 @@
       <c r="G67" s="21" t="n">
         <v>0.002697</v>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="H67" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -10855,7 +10873,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D68" s="25" t="inlineStr">
+      <c r="D68" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10873,7 +10891,7 @@
       <c r="G68" s="21" t="n">
         <v>0.003889</v>
       </c>
-      <c r="H68" s="25" t="inlineStr">
+      <c r="H68" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -10931,7 +10949,7 @@
           <t>Components.BodyMountedSolarArrayPlusYUnit</t>
         </is>
       </c>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D69" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -10949,7 +10967,7 @@
       <c r="G69" s="21" t="n">
         <v>0.001192</v>
       </c>
-      <c r="H69" s="18" t="inlineStr">
+      <c r="H69" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -11007,7 +11025,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D70" s="25" t="inlineStr">
+      <c r="D70" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -11025,7 +11043,7 @@
       <c r="G70" s="21" t="n">
         <v>0.06224</v>
       </c>
-      <c r="H70" s="25" t="inlineStr">
+      <c r="H70" s="63" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -11083,7 +11101,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -11101,7 +11119,7 @@
       <c r="G71" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="H71" s="18" t="inlineStr">
+      <c r="H71" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11159,7 +11177,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D72" s="25" t="inlineStr">
+      <c r="D72" s="63" t="inlineStr">
         <is>
           <t>Life</t>
         </is>
@@ -11177,7 +11195,7 @@
       <c r="G72" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H72" s="25" t="inlineStr">
+      <c r="H72" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11235,7 +11253,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D73" s="18" t="inlineStr">
+      <c r="D73" s="62" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
@@ -11253,7 +11271,7 @@
       <c r="G73" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="H73" s="18" t="inlineStr">
+      <c r="H73" s="62" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -11307,7 +11325,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D74" s="25" t="inlineStr">
+      <c r="D74" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -11325,7 +11343,7 @@
       <c r="G74" s="21" t="n">
         <v>0.96</v>
       </c>
-      <c r="H74" s="25" t="inlineStr">
+      <c r="H74" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11383,7 +11401,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D75" s="18" t="inlineStr">
+      <c r="D75" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -11401,7 +11419,7 @@
       <c r="G75" s="21" t="n">
         <v>0.9</v>
       </c>
-      <c r="H75" s="18" t="inlineStr">
+      <c r="H75" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11459,7 +11477,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D76" s="25" t="inlineStr">
+      <c r="D76" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -11477,7 +11495,7 @@
       <c r="G76" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H76" s="25" t="inlineStr">
+      <c r="H76" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11535,7 +11553,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="D77" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -11553,7 +11571,7 @@
       <c r="G77" s="21" t="n">
         <v>0.85</v>
       </c>
-      <c r="H77" s="18" t="inlineStr">
+      <c r="H77" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11611,7 +11629,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D78" s="25" t="inlineStr">
+      <c r="D78" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -11629,7 +11647,7 @@
       <c r="G78" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="H78" s="25" t="inlineStr">
+      <c r="H78" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -11683,7 +11701,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D79" s="18" t="inlineStr">
+      <c r="D79" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -11701,7 +11719,7 @@
       <c r="G79" s="21" t="n">
         <v>0.065</v>
       </c>
-      <c r="H79" s="18" t="inlineStr">
+      <c r="H79" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -11755,7 +11773,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D80" s="25" t="inlineStr">
+      <c r="D80" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -11773,7 +11791,7 @@
       <c r="G80" s="21" t="n">
         <v>470</v>
       </c>
-      <c r="H80" s="25" t="inlineStr">
+      <c r="H80" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -11827,7 +11845,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="D81" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -11845,7 +11863,7 @@
       <c r="G81" s="21" t="n">
         <v>-1</v>
       </c>
-      <c r="H81" s="18" t="inlineStr">
+      <c r="H81" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11903,7 +11921,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D82" s="25" t="inlineStr">
+      <c r="D82" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -11921,7 +11939,7 @@
       <c r="G82" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="25" t="inlineStr">
+      <c r="H82" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -11979,7 +11997,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D83" s="18" t="inlineStr">
+      <c r="D83" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -11997,7 +12015,7 @@
       <c r="G83" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="18" t="inlineStr">
+      <c r="H83" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -12055,7 +12073,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D84" s="25" t="inlineStr">
+      <c r="D84" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12073,7 +12091,7 @@
       <c r="G84" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="H84" s="25" t="inlineStr">
+      <c r="H84" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -12131,7 +12149,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D85" s="18" t="inlineStr">
+      <c r="D85" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12149,7 +12167,7 @@
       <c r="G85" s="21" t="n">
         <v>-0.113</v>
       </c>
-      <c r="H85" s="18" t="inlineStr">
+      <c r="H85" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -12207,7 +12225,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D86" s="25" t="inlineStr">
+      <c r="D86" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12225,7 +12243,7 @@
       <c r="G86" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="25" t="inlineStr">
+      <c r="H86" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -12283,7 +12301,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D87" s="18" t="inlineStr">
+      <c r="D87" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12301,7 +12319,7 @@
       <c r="G87" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="18" t="inlineStr">
+      <c r="H87" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -12359,7 +12377,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D88" s="25" t="inlineStr">
+      <c r="D88" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12377,7 +12395,7 @@
       <c r="G88" s="21" t="n">
         <v>0.003472</v>
       </c>
-      <c r="H88" s="25" t="inlineStr">
+      <c r="H88" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -12435,7 +12453,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D89" s="18" t="inlineStr">
+      <c r="D89" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12453,7 +12471,7 @@
       <c r="G89" s="21" t="n">
         <v>0.002408</v>
       </c>
-      <c r="H89" s="18" t="inlineStr">
+      <c r="H89" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -12511,7 +12529,7 @@
           <t>Components.BodyMountedSolarArrayMinusXUnit</t>
         </is>
       </c>
-      <c r="D90" s="25" t="inlineStr">
+      <c r="D90" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -12529,7 +12547,7 @@
       <c r="G90" s="21" t="n">
         <v>0.001064</v>
       </c>
-      <c r="H90" s="25" t="inlineStr">
+      <c r="H90" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -12587,7 +12605,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D91" s="18" t="inlineStr">
+      <c r="D91" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -12605,7 +12623,7 @@
       <c r="G91" s="21" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H91" s="18" t="inlineStr">
+      <c r="H91" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -12663,7 +12681,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D92" s="25" t="inlineStr">
+      <c r="D92" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -12681,7 +12699,7 @@
       <c r="G92" s="21" t="n">
         <v>10.2</v>
       </c>
-      <c r="H92" s="25" t="inlineStr">
+      <c r="H92" s="63" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -12735,7 +12753,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="D93" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -12753,7 +12771,7 @@
       <c r="G93" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="H93" s="18" t="inlineStr">
+      <c r="H93" s="62" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -12807,7 +12825,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D94" s="25" t="inlineStr">
+      <c r="D94" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -12825,7 +12843,7 @@
       <c r="G94" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="H94" s="25" t="inlineStr">
+      <c r="H94" s="63" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -12879,7 +12897,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D95" s="18" t="inlineStr">
+      <c r="D95" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -12897,7 +12915,7 @@
       <c r="G95" s="21" t="n">
         <v>96</v>
       </c>
-      <c r="H95" s="18" t="inlineStr">
+      <c r="H95" s="62" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -12951,7 +12969,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D96" s="25" t="inlineStr">
+      <c r="D96" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -12969,7 +12987,7 @@
       <c r="G96" s="21" t="n">
         <v>0.035</v>
       </c>
-      <c r="H96" s="25" t="inlineStr">
+      <c r="H96" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -13023,7 +13041,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D97" s="18" t="inlineStr">
+      <c r="D97" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13041,7 +13059,7 @@
       <c r="G97" s="21" t="n">
         <v>0.65</v>
       </c>
-      <c r="H97" s="18" t="inlineStr">
+      <c r="H97" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -13099,7 +13117,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D98" s="25" t="inlineStr">
+      <c r="D98" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13117,7 +13135,7 @@
       <c r="G98" s="21" t="n">
         <v>0.91</v>
       </c>
-      <c r="H98" s="25" t="inlineStr">
+      <c r="H98" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13175,7 +13193,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D99" s="18" t="inlineStr">
+      <c r="D99" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13193,7 +13211,7 @@
       <c r="G99" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="H99" s="18" t="inlineStr">
+      <c r="H99" s="62" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -13247,7 +13265,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D100" s="25" t="inlineStr">
+      <c r="D100" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13265,7 +13283,7 @@
       <c r="G100" s="21" t="n">
         <v>5.25</v>
       </c>
-      <c r="H100" s="25" t="inlineStr">
+      <c r="H100" s="63" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -13319,7 +13337,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
+      <c r="D101" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13337,7 +13355,7 @@
       <c r="G101" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="H101" s="18" t="inlineStr">
+      <c r="H101" s="62" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -13391,7 +13409,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D102" s="25" t="inlineStr">
+      <c r="D102" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13409,7 +13427,7 @@
       <c r="G102" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="H102" s="25" t="inlineStr">
+      <c r="H102" s="63" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -13463,7 +13481,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D103" s="18" t="inlineStr">
+      <c r="D103" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13481,7 +13499,7 @@
       <c r="G103" s="21" t="n">
         <v>0.025</v>
       </c>
-      <c r="H103" s="18" t="inlineStr">
+      <c r="H103" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -13535,7 +13553,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D104" s="25" t="inlineStr">
+      <c r="D104" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13553,7 +13571,7 @@
       <c r="G104" s="21" t="n">
         <v>0.45</v>
       </c>
-      <c r="H104" s="25" t="inlineStr">
+      <c r="H104" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -13607,7 +13625,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D105" s="18" t="inlineStr">
+      <c r="D105" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13625,7 +13643,7 @@
       <c r="G105" s="21" t="n">
         <v>0.89</v>
       </c>
-      <c r="H105" s="18" t="inlineStr">
+      <c r="H105" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -13683,7 +13701,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D106" s="25" t="inlineStr">
+      <c r="D106" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13701,7 +13719,7 @@
       <c r="G106" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="H106" s="25" t="inlineStr">
+      <c r="H106" s="63" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -13755,7 +13773,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D107" s="18" t="inlineStr">
+      <c r="D107" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13773,7 +13791,7 @@
       <c r="G107" s="21" t="n">
         <v>3.45</v>
       </c>
-      <c r="H107" s="18" t="inlineStr">
+      <c r="H107" s="62" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -13827,7 +13845,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D108" s="25" t="inlineStr">
+      <c r="D108" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13845,7 +13863,7 @@
       <c r="G108" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="H108" s="25" t="inlineStr">
+      <c r="H108" s="63" t="inlineStr">
         <is>
           <t>W</t>
         </is>
@@ -13899,7 +13917,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D109" s="18" t="inlineStr">
+      <c r="D109" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13917,7 +13935,7 @@
       <c r="G109" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="H109" s="18" t="inlineStr">
+      <c r="H109" s="62" t="inlineStr">
         <is>
           <t>V</t>
         </is>
@@ -13971,7 +13989,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D110" s="25" t="inlineStr">
+      <c r="D110" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -13989,7 +14007,7 @@
       <c r="G110" s="21" t="n">
         <v>0.03</v>
       </c>
-      <c r="H110" s="25" t="inlineStr">
+      <c r="H110" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -14043,7 +14061,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D111" s="18" t="inlineStr">
+      <c r="D111" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -14061,7 +14079,7 @@
       <c r="G111" s="21" t="n">
         <v>0.5</v>
       </c>
-      <c r="H111" s="18" t="inlineStr">
+      <c r="H111" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -14115,7 +14133,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D112" s="25" t="inlineStr">
+      <c r="D112" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -14133,7 +14151,7 @@
       <c r="G112" s="21" t="n">
         <v>93.34999999999999</v>
       </c>
-      <c r="H112" s="25" t="inlineStr">
+      <c r="H112" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -14187,7 +14205,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D113" s="18" t="inlineStr">
+      <c r="D113" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -14205,7 +14223,7 @@
       <c r="G113" s="21" t="n">
         <v>680</v>
       </c>
-      <c r="H113" s="18" t="inlineStr">
+      <c r="H113" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -14259,7 +14277,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D114" s="25" t="inlineStr">
+      <c r="D114" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -14277,7 +14295,7 @@
       <c r="G114" s="21" t="n">
         <v>0.2</v>
       </c>
-      <c r="H114" s="25" t="inlineStr">
+      <c r="H114" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -14331,7 +14349,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D115" s="18" t="inlineStr">
+      <c r="D115" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14349,7 +14367,7 @@
       <c r="G115" s="21" t="n">
         <v>0.72</v>
       </c>
-      <c r="H115" s="18" t="inlineStr">
+      <c r="H115" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -14407,7 +14425,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D116" s="25" t="inlineStr">
+      <c r="D116" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14425,7 +14443,7 @@
       <c r="G116" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H116" s="25" t="inlineStr">
+      <c r="H116" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -14483,7 +14501,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D117" s="18" t="inlineStr">
+      <c r="D117" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14501,7 +14519,7 @@
       <c r="G117" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H117" s="18" t="inlineStr">
+      <c r="H117" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -14559,7 +14577,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D118" s="25" t="inlineStr">
+      <c r="D118" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14577,7 +14595,7 @@
       <c r="G118" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H118" s="25" t="inlineStr">
+      <c r="H118" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -14635,7 +14653,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D119" s="18" t="inlineStr">
+      <c r="D119" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14653,7 +14671,7 @@
       <c r="G119" s="21" t="n">
         <v>0.002</v>
       </c>
-      <c r="H119" s="18" t="inlineStr">
+      <c r="H119" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -14711,7 +14729,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D120" s="25" t="inlineStr">
+      <c r="D120" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14729,7 +14747,7 @@
       <c r="G120" s="21" t="n">
         <v>0.003</v>
       </c>
-      <c r="H120" s="25" t="inlineStr">
+      <c r="H120" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -14787,7 +14805,7 @@
           <t>Components.PowerConditioningUnit</t>
         </is>
       </c>
-      <c r="D121" s="18" t="inlineStr">
+      <c r="D121" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -14805,7 +14823,7 @@
       <c r="G121" s="21" t="n">
         <v>0.002</v>
       </c>
-      <c r="H121" s="18" t="inlineStr">
+      <c r="H121" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -14935,7 +14953,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D123" s="18" t="inlineStr">
+      <c r="D123" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -14953,7 +14971,7 @@
       <c r="G123" s="21" t="n">
         <v>210</v>
       </c>
-      <c r="H123" s="18" t="inlineStr">
+      <c r="H123" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -15007,7 +15025,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D124" s="25" t="inlineStr">
+      <c r="D124" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -15025,7 +15043,7 @@
       <c r="G124" s="21" t="n">
         <v>0.38</v>
       </c>
-      <c r="H124" s="25" t="inlineStr">
+      <c r="H124" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -15079,7 +15097,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D125" s="18" t="inlineStr">
+      <c r="D125" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15097,7 +15115,7 @@
       <c r="G125" s="21" t="n">
         <v>0.39</v>
       </c>
-      <c r="H125" s="18" t="inlineStr">
+      <c r="H125" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -15155,7 +15173,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D126" s="25" t="inlineStr">
+      <c r="D126" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15173,7 +15191,7 @@
       <c r="G126" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H126" s="25" t="inlineStr">
+      <c r="H126" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -15231,7 +15249,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D127" s="18" t="inlineStr">
+      <c r="D127" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15249,7 +15267,7 @@
       <c r="G127" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H127" s="18" t="inlineStr">
+      <c r="H127" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -15307,7 +15325,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D128" s="25" t="inlineStr">
+      <c r="D128" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15325,7 +15343,7 @@
       <c r="G128" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H128" s="25" t="inlineStr">
+      <c r="H128" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -15383,7 +15401,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D129" s="18" t="inlineStr">
+      <c r="D129" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15401,7 +15419,7 @@
       <c r="G129" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="H129" s="18" t="inlineStr">
+      <c r="H129" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -15459,7 +15477,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D130" s="25" t="inlineStr">
+      <c r="D130" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15477,7 +15495,7 @@
       <c r="G130" s="21" t="n">
         <v>0.0012</v>
       </c>
-      <c r="H130" s="25" t="inlineStr">
+      <c r="H130" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -15535,7 +15553,7 @@
           <t>Components.GNCComputerUnit</t>
         </is>
       </c>
-      <c r="D131" s="18" t="inlineStr">
+      <c r="D131" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15553,7 +15571,7 @@
       <c r="G131" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="H131" s="18" t="inlineStr">
+      <c r="H131" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -15611,7 +15629,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D132" s="25" t="inlineStr">
+      <c r="D132" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -15629,7 +15647,7 @@
       <c r="G132" s="21" t="n">
         <v>628.3185307</v>
       </c>
-      <c r="H132" s="25" t="inlineStr">
+      <c r="H132" s="63" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
@@ -15687,7 +15705,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D133" s="18" t="inlineStr">
+      <c r="D133" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -15705,7 +15723,7 @@
       <c r="G133" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H133" s="18" t="inlineStr">
+      <c r="H133" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -15763,7 +15781,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D134" s="25" t="inlineStr">
+      <c r="D134" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -15781,7 +15799,7 @@
       <c r="G134" s="21" t="n">
         <v>253</v>
       </c>
-      <c r="H134" s="25" t="inlineStr">
+      <c r="H134" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -15835,7 +15853,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D135" s="18" t="inlineStr">
+      <c r="D135" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -15853,7 +15871,7 @@
       <c r="G135" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="H135" s="18" t="inlineStr">
+      <c r="H135" s="62" t="inlineStr">
         <is>
           <t>N·m</t>
         </is>
@@ -15911,7 +15929,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D136" s="25" t="inlineStr">
+      <c r="D136" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -15929,7 +15947,7 @@
       <c r="G136" s="21" t="n">
         <v>9.500000000000001e-05</v>
       </c>
-      <c r="H136" s="25" t="inlineStr">
+      <c r="H136" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -15983,7 +16001,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D137" s="18" t="inlineStr">
+      <c r="D137" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16001,7 +16019,7 @@
       <c r="G137" s="21" t="n">
         <v>1.1e-07</v>
       </c>
-      <c r="H137" s="18" t="inlineStr">
+      <c r="H137" s="62" t="inlineStr">
         <is>
           <t>N·m·s/rad</t>
         </is>
@@ -16055,7 +16073,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D138" s="25" t="inlineStr">
+      <c r="D138" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -16073,7 +16091,7 @@
       <c r="G138" s="21" t="n">
         <v>112</v>
       </c>
-      <c r="H138" s="25" t="inlineStr">
+      <c r="H138" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -16127,7 +16145,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D139" s="18" t="inlineStr">
+      <c r="D139" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -16145,7 +16163,7 @@
       <c r="G139" s="21" t="n">
         <v>0.075</v>
       </c>
-      <c r="H139" s="18" t="inlineStr">
+      <c r="H139" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -16199,7 +16217,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D140" s="25" t="inlineStr">
+      <c r="D140" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16217,7 +16235,7 @@
       <c r="G140" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H140" s="25" t="inlineStr">
+      <c r="H140" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -16275,7 +16293,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D141" s="18" t="inlineStr">
+      <c r="D141" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16293,7 +16311,7 @@
       <c r="G141" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H141" s="18" t="inlineStr">
+      <c r="H141" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -16351,7 +16369,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D142" s="25" t="inlineStr">
+      <c r="D142" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16369,7 +16387,7 @@
       <c r="G142" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H142" s="25" t="inlineStr">
+      <c r="H142" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -16427,7 +16445,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D143" s="18" t="inlineStr">
+      <c r="D143" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16445,7 +16463,7 @@
       <c r="G143" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H143" s="18" t="inlineStr">
+      <c r="H143" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -16503,7 +16521,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D144" s="25" t="inlineStr">
+      <c r="D144" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16521,7 +16539,7 @@
       <c r="G144" s="21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="H144" s="25" t="inlineStr">
+      <c r="H144" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -16579,7 +16597,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D145" s="18" t="inlineStr">
+      <c r="D145" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16597,7 +16615,7 @@
       <c r="G145" s="21" t="n">
         <v>-0.04</v>
       </c>
-      <c r="H145" s="18" t="inlineStr">
+      <c r="H145" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -16655,7 +16673,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D146" s="25" t="inlineStr">
+      <c r="D146" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16673,7 +16691,7 @@
       <c r="G146" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H146" s="25" t="inlineStr">
+      <c r="H146" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -16731,7 +16749,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D147" s="18" t="inlineStr">
+      <c r="D147" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16749,7 +16767,7 @@
       <c r="G147" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H147" s="18" t="inlineStr">
+      <c r="H147" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -16807,7 +16825,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D148" s="25" t="inlineStr">
+      <c r="D148" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16825,7 +16843,7 @@
       <c r="G148" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H148" s="25" t="inlineStr">
+      <c r="H148" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -16883,7 +16901,7 @@
           <t>Components.ReactionWheelXUnit</t>
         </is>
       </c>
-      <c r="D149" s="18" t="inlineStr">
+      <c r="D149" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -16901,7 +16919,7 @@
       <c r="G149" s="21" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="H149" s="18" t="inlineStr">
+      <c r="H149" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -16959,7 +16977,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D150" s="25" t="inlineStr">
+      <c r="D150" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -16977,7 +16995,7 @@
       <c r="G150" s="21" t="n">
         <v>628.3185307</v>
       </c>
-      <c r="H150" s="25" t="inlineStr">
+      <c r="H150" s="63" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
@@ -17035,7 +17053,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D151" s="18" t="inlineStr">
+      <c r="D151" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -17053,7 +17071,7 @@
       <c r="G151" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H151" s="18" t="inlineStr">
+      <c r="H151" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17111,7 +17129,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D152" s="25" t="inlineStr">
+      <c r="D152" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -17129,7 +17147,7 @@
       <c r="G152" s="21" t="n">
         <v>337</v>
       </c>
-      <c r="H152" s="25" t="inlineStr">
+      <c r="H152" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -17183,7 +17201,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D153" s="18" t="inlineStr">
+      <c r="D153" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -17201,7 +17219,7 @@
       <c r="G153" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="H153" s="18" t="inlineStr">
+      <c r="H153" s="62" t="inlineStr">
         <is>
           <t>N·m</t>
         </is>
@@ -17259,7 +17277,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D154" s="25" t="inlineStr">
+      <c r="D154" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17277,7 +17295,7 @@
       <c r="G154" s="21" t="n">
         <v>9.8e-05</v>
       </c>
-      <c r="H154" s="25" t="inlineStr">
+      <c r="H154" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -17331,7 +17349,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D155" s="18" t="inlineStr">
+      <c r="D155" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17349,7 +17367,7 @@
       <c r="G155" s="21" t="n">
         <v>1.3e-07</v>
       </c>
-      <c r="H155" s="18" t="inlineStr">
+      <c r="H155" s="62" t="inlineStr">
         <is>
           <t>N·m·s/rad</t>
         </is>
@@ -17403,7 +17421,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D156" s="25" t="inlineStr">
+      <c r="D156" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -17421,7 +17439,7 @@
       <c r="G156" s="21" t="n">
         <v>108</v>
       </c>
-      <c r="H156" s="25" t="inlineStr">
+      <c r="H156" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -17475,7 +17493,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D157" s="18" t="inlineStr">
+      <c r="D157" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -17493,7 +17511,7 @@
       <c r="G157" s="21" t="n">
         <v>0.35</v>
       </c>
-      <c r="H157" s="18" t="inlineStr">
+      <c r="H157" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -17547,7 +17565,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D158" s="25" t="inlineStr">
+      <c r="D158" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17565,7 +17583,7 @@
       <c r="G158" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H158" s="25" t="inlineStr">
+      <c r="H158" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17623,7 +17641,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D159" s="18" t="inlineStr">
+      <c r="D159" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17641,7 +17659,7 @@
       <c r="G159" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H159" s="18" t="inlineStr">
+      <c r="H159" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17699,7 +17717,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D160" s="25" t="inlineStr">
+      <c r="D160" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17717,7 +17735,7 @@
       <c r="G160" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H160" s="25" t="inlineStr">
+      <c r="H160" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -17775,7 +17793,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D161" s="18" t="inlineStr">
+      <c r="D161" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17793,7 +17811,7 @@
       <c r="G161" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H161" s="18" t="inlineStr">
+      <c r="H161" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -17851,7 +17869,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D162" s="25" t="inlineStr">
+      <c r="D162" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17869,7 +17887,7 @@
       <c r="G162" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="H162" s="25" t="inlineStr">
+      <c r="H162" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -17927,7 +17945,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D163" s="18" t="inlineStr">
+      <c r="D163" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -17945,7 +17963,7 @@
       <c r="G163" s="21" t="n">
         <v>-0.04</v>
       </c>
-      <c r="H163" s="18" t="inlineStr">
+      <c r="H163" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -18003,7 +18021,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D164" s="25" t="inlineStr">
+      <c r="D164" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18021,7 +18039,7 @@
       <c r="G164" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H164" s="25" t="inlineStr">
+      <c r="H164" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -18079,7 +18097,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D165" s="18" t="inlineStr">
+      <c r="D165" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18097,7 +18115,7 @@
       <c r="G165" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H165" s="18" t="inlineStr">
+      <c r="H165" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -18155,7 +18173,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D166" s="25" t="inlineStr">
+      <c r="D166" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18173,7 +18191,7 @@
       <c r="G166" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H166" s="25" t="inlineStr">
+      <c r="H166" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -18231,7 +18249,7 @@
           <t>Components.ReactionWheelYUnit</t>
         </is>
       </c>
-      <c r="D167" s="18" t="inlineStr">
+      <c r="D167" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18249,7 +18267,7 @@
       <c r="G167" s="21" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="H167" s="18" t="inlineStr">
+      <c r="H167" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -18307,7 +18325,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D168" s="25" t="inlineStr">
+      <c r="D168" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -18325,7 +18343,7 @@
       <c r="G168" s="21" t="n">
         <v>628.3185307</v>
       </c>
-      <c r="H168" s="25" t="inlineStr">
+      <c r="H168" s="63" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
@@ -18383,7 +18401,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D169" s="18" t="inlineStr">
+      <c r="D169" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -18401,7 +18419,7 @@
       <c r="G169" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H169" s="18" t="inlineStr">
+      <c r="H169" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -18459,7 +18477,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D170" s="25" t="inlineStr">
+      <c r="D170" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -18477,7 +18495,7 @@
       <c r="G170" s="21" t="n">
         <v>270</v>
       </c>
-      <c r="H170" s="25" t="inlineStr">
+      <c r="H170" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -18531,7 +18549,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D171" s="18" t="inlineStr">
+      <c r="D171" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -18549,7 +18567,7 @@
       <c r="G171" s="21" t="n">
         <v>0.01</v>
       </c>
-      <c r="H171" s="18" t="inlineStr">
+      <c r="H171" s="62" t="inlineStr">
         <is>
           <t>N·m</t>
         </is>
@@ -18607,7 +18625,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D172" s="25" t="inlineStr">
+      <c r="D172" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18625,7 +18643,7 @@
       <c r="G172" s="21" t="n">
         <v>9.3e-05</v>
       </c>
-      <c r="H172" s="25" t="inlineStr">
+      <c r="H172" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -18679,7 +18697,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D173" s="18" t="inlineStr">
+      <c r="D173" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18697,7 +18715,7 @@
       <c r="G173" s="21" t="n">
         <v>9e-08</v>
       </c>
-      <c r="H173" s="18" t="inlineStr">
+      <c r="H173" s="62" t="inlineStr">
         <is>
           <t>N·m·s/rad</t>
         </is>
@@ -18751,7 +18769,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D174" s="25" t="inlineStr">
+      <c r="D174" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -18769,7 +18787,7 @@
       <c r="G174" s="21" t="n">
         <v>115</v>
       </c>
-      <c r="H174" s="25" t="inlineStr">
+      <c r="H174" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -18823,7 +18841,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D175" s="18" t="inlineStr">
+      <c r="D175" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -18841,7 +18859,7 @@
       <c r="G175" s="21" t="n">
         <v>0.075</v>
       </c>
-      <c r="H175" s="18" t="inlineStr">
+      <c r="H175" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -18895,7 +18913,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D176" s="25" t="inlineStr">
+      <c r="D176" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18913,7 +18931,7 @@
       <c r="G176" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H176" s="25" t="inlineStr">
+      <c r="H176" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -18971,7 +18989,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D177" s="18" t="inlineStr">
+      <c r="D177" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -18989,7 +19007,7 @@
       <c r="G177" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H177" s="18" t="inlineStr">
+      <c r="H177" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19047,7 +19065,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D178" s="25" t="inlineStr">
+      <c r="D178" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19065,7 +19083,7 @@
       <c r="G178" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H178" s="25" t="inlineStr">
+      <c r="H178" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19123,7 +19141,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D179" s="18" t="inlineStr">
+      <c r="D179" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19141,7 +19159,7 @@
       <c r="G179" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H179" s="18" t="inlineStr">
+      <c r="H179" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -19199,7 +19217,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D180" s="25" t="inlineStr">
+      <c r="D180" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19217,7 +19235,7 @@
       <c r="G180" s="21" t="n">
         <v>-0.06</v>
       </c>
-      <c r="H180" s="25" t="inlineStr">
+      <c r="H180" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -19275,7 +19293,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D181" s="18" t="inlineStr">
+      <c r="D181" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19293,7 +19311,7 @@
       <c r="G181" s="21" t="n">
         <v>0.04</v>
       </c>
-      <c r="H181" s="18" t="inlineStr">
+      <c r="H181" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -19351,7 +19369,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D182" s="25" t="inlineStr">
+      <c r="D182" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19369,7 +19387,7 @@
       <c r="G182" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H182" s="25" t="inlineStr">
+      <c r="H182" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -19427,7 +19445,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D183" s="18" t="inlineStr">
+      <c r="D183" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19445,7 +19463,7 @@
       <c r="G183" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H183" s="18" t="inlineStr">
+      <c r="H183" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -19503,7 +19521,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D184" s="25" t="inlineStr">
+      <c r="D184" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19521,7 +19539,7 @@
       <c r="G184" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H184" s="25" t="inlineStr">
+      <c r="H184" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -19579,7 +19597,7 @@
           <t>Components.ReactionWheelZUnit</t>
         </is>
       </c>
-      <c r="D185" s="18" t="inlineStr">
+      <c r="D185" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19597,7 +19615,7 @@
       <c r="G185" s="21" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="H185" s="18" t="inlineStr">
+      <c r="H185" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -19655,7 +19673,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D186" s="25" t="inlineStr">
+      <c r="D186" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -19673,7 +19691,7 @@
       <c r="G186" s="21" t="n">
         <v>628.3185307</v>
       </c>
-      <c r="H186" s="25" t="inlineStr">
+      <c r="H186" s="63" t="inlineStr">
         <is>
           <t>rad/s</t>
         </is>
@@ -19731,7 +19749,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D187" s="18" t="inlineStr">
+      <c r="D187" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -19749,7 +19767,7 @@
       <c r="G187" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="H187" s="18" t="inlineStr">
+      <c r="H187" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -19807,7 +19825,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D188" s="25" t="inlineStr">
+      <c r="D188" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -19825,7 +19843,7 @@
       <c r="G188" s="21" t="n">
         <v>1000000</v>
       </c>
-      <c r="H188" s="25" t="inlineStr">
+      <c r="H188" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -19879,7 +19897,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D189" s="18" t="inlineStr">
+      <c r="D189" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -19897,7 +19915,7 @@
       <c r="G189" s="21" t="n">
         <v>0.0038</v>
       </c>
-      <c r="H189" s="18" t="inlineStr">
+      <c r="H189" s="62" t="inlineStr">
         <is>
           <t>N·m</t>
         </is>
@@ -19955,7 +19973,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D190" s="25" t="inlineStr">
+      <c r="D190" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -19973,7 +19991,7 @@
       <c r="G190" s="21" t="n">
         <v>0.000102</v>
       </c>
-      <c r="H190" s="25" t="inlineStr">
+      <c r="H190" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -20027,7 +20045,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D191" s="18" t="inlineStr">
+      <c r="D191" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20045,7 +20063,7 @@
       <c r="G191" s="21" t="n">
         <v>1.4e-07</v>
       </c>
-      <c r="H191" s="18" t="inlineStr">
+      <c r="H191" s="62" t="inlineStr">
         <is>
           <t>N·m·s/rad</t>
         </is>
@@ -20099,7 +20117,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D192" s="25" t="inlineStr">
+      <c r="D192" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -20117,7 +20135,7 @@
       <c r="G192" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="H192" s="25" t="inlineStr">
+      <c r="H192" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -20171,7 +20189,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D193" s="18" t="inlineStr">
+      <c r="D193" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -20189,7 +20207,7 @@
       <c r="G193" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="H193" s="18" t="inlineStr">
+      <c r="H193" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -20243,7 +20261,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D194" s="25" t="inlineStr">
+      <c r="D194" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20261,7 +20279,7 @@
       <c r="G194" s="21" t="n">
         <v>0.577350269</v>
       </c>
-      <c r="H194" s="25" t="inlineStr">
+      <c r="H194" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -20319,7 +20337,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D195" s="18" t="inlineStr">
+      <c r="D195" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20337,7 +20355,7 @@
       <c r="G195" s="21" t="n">
         <v>0.577350269</v>
       </c>
-      <c r="H195" s="18" t="inlineStr">
+      <c r="H195" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -20395,7 +20413,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D196" s="25" t="inlineStr">
+      <c r="D196" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20413,7 +20431,7 @@
       <c r="G196" s="21" t="n">
         <v>0.577350269</v>
       </c>
-      <c r="H196" s="25" t="inlineStr">
+      <c r="H196" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -20471,7 +20489,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D197" s="18" t="inlineStr">
+      <c r="D197" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20489,7 +20507,7 @@
       <c r="G197" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H197" s="18" t="inlineStr">
+      <c r="H197" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -20547,7 +20565,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D198" s="25" t="inlineStr">
+      <c r="D198" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20565,7 +20583,7 @@
       <c r="G198" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="H198" s="25" t="inlineStr">
+      <c r="H198" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -20623,7 +20641,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D199" s="18" t="inlineStr">
+      <c r="D199" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20641,7 +20659,7 @@
       <c r="G199" s="21" t="n">
         <v>0.04</v>
       </c>
-      <c r="H199" s="18" t="inlineStr">
+      <c r="H199" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -20699,7 +20717,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D200" s="25" t="inlineStr">
+      <c r="D200" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20717,7 +20735,7 @@
       <c r="G200" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H200" s="25" t="inlineStr">
+      <c r="H200" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -20775,7 +20793,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D201" s="18" t="inlineStr">
+      <c r="D201" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20793,7 +20811,7 @@
       <c r="G201" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H201" s="18" t="inlineStr">
+      <c r="H201" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -20851,7 +20869,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D202" s="25" t="inlineStr">
+      <c r="D202" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20869,7 +20887,7 @@
       <c r="G202" s="21" t="n">
         <v>5.1e-05</v>
       </c>
-      <c r="H202" s="25" t="inlineStr">
+      <c r="H202" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -20927,7 +20945,7 @@
           <t>Components.ReactionWheelSUnit</t>
         </is>
       </c>
-      <c r="D203" s="18" t="inlineStr">
+      <c r="D203" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -20945,7 +20963,7 @@
       <c r="G203" s="21" t="n">
         <v>7.499999999999999e-05</v>
       </c>
-      <c r="H203" s="18" t="inlineStr">
+      <c r="H203" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -21003,7 +21021,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D204" s="25" t="inlineStr">
+      <c r="D204" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -21021,7 +21039,7 @@
       <c r="G204" s="21" t="n">
         <v>51.9</v>
       </c>
-      <c r="H204" s="25" t="inlineStr">
+      <c r="H204" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -21075,7 +21093,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D205" s="18" t="inlineStr">
+      <c r="D205" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -21093,7 +21111,7 @@
       <c r="G205" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="H205" s="18" t="inlineStr">
+      <c r="H205" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -21147,7 +21165,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D206" s="25" t="inlineStr">
+      <c r="D206" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -21165,7 +21183,7 @@
       <c r="G206" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H206" s="25" t="inlineStr">
+      <c r="H206" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -21219,7 +21237,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D207" s="18" t="inlineStr">
+      <c r="D207" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21237,7 +21255,7 @@
       <c r="G207" s="21" t="n">
         <v>0.48</v>
       </c>
-      <c r="H207" s="18" t="inlineStr">
+      <c r="H207" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -21295,7 +21313,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D208" s="25" t="inlineStr">
+      <c r="D208" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21313,7 +21331,7 @@
       <c r="G208" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H208" s="25" t="inlineStr">
+      <c r="H208" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -21371,7 +21389,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D209" s="18" t="inlineStr">
+      <c r="D209" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21389,7 +21407,7 @@
       <c r="G209" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H209" s="18" t="inlineStr">
+      <c r="H209" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -21447,7 +21465,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D210" s="25" t="inlineStr">
+      <c r="D210" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21465,7 +21483,7 @@
       <c r="G210" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H210" s="25" t="inlineStr">
+      <c r="H210" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -21523,7 +21541,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D211" s="18" t="inlineStr">
+      <c r="D211" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21541,7 +21559,7 @@
       <c r="G211" s="21" t="n">
         <v>0.0015</v>
       </c>
-      <c r="H211" s="18" t="inlineStr">
+      <c r="H211" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -21599,7 +21617,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D212" s="25" t="inlineStr">
+      <c r="D212" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21617,7 +21635,7 @@
       <c r="G212" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="H212" s="25" t="inlineStr">
+      <c r="H212" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -21675,7 +21693,7 @@
           <t>Components.StarTrackerYUnit</t>
         </is>
       </c>
-      <c r="D213" s="18" t="inlineStr">
+      <c r="D213" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -21693,7 +21711,7 @@
       <c r="G213" s="21" t="n">
         <v>0.0015</v>
       </c>
-      <c r="H213" s="18" t="inlineStr">
+      <c r="H213" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -21751,7 +21769,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D214" s="25" t="inlineStr">
+      <c r="D214" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -21769,7 +21787,7 @@
       <c r="G214" s="21" t="n">
         <v>51.9</v>
       </c>
-      <c r="H214" s="25" t="inlineStr">
+      <c r="H214" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -21823,7 +21841,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D215" s="18" t="inlineStr">
+      <c r="D215" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -21841,7 +21859,7 @@
       <c r="G215" s="21" t="n">
         <v>135</v>
       </c>
-      <c r="H215" s="18" t="inlineStr">
+      <c r="H215" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -21895,7 +21913,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D216" s="25" t="inlineStr">
+      <c r="D216" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -21913,7 +21931,7 @@
       <c r="G216" s="21" t="n">
         <v>9.5</v>
       </c>
-      <c r="H216" s="25" t="inlineStr">
+      <c r="H216" s="63" t="inlineStr">
         <is>
           <t>K/W</t>
         </is>
@@ -21967,7 +21985,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D217" s="18" t="inlineStr">
+      <c r="D217" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -21985,7 +22003,7 @@
       <c r="G217" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H217" s="18" t="inlineStr">
+      <c r="H217" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -22039,7 +22057,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D218" s="25" t="inlineStr">
+      <c r="D218" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22057,7 +22075,7 @@
       <c r="G218" s="21" t="n">
         <v>0.52</v>
       </c>
-      <c r="H218" s="25" t="inlineStr">
+      <c r="H218" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -22115,7 +22133,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D219" s="18" t="inlineStr">
+      <c r="D219" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22133,7 +22151,7 @@
       <c r="G219" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H219" s="18" t="inlineStr">
+      <c r="H219" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -22191,7 +22209,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D220" s="25" t="inlineStr">
+      <c r="D220" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22209,7 +22227,7 @@
       <c r="G220" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H220" s="25" t="inlineStr">
+      <c r="H220" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -22267,7 +22285,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D221" s="18" t="inlineStr">
+      <c r="D221" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22285,7 +22303,7 @@
       <c r="G221" s="21" t="n">
         <v>0.11</v>
       </c>
-      <c r="H221" s="18" t="inlineStr">
+      <c r="H221" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -22343,7 +22361,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D222" s="25" t="inlineStr">
+      <c r="D222" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22361,7 +22379,7 @@
       <c r="G222" s="21" t="n">
         <v>0.0016</v>
       </c>
-      <c r="H222" s="25" t="inlineStr">
+      <c r="H222" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -22419,7 +22437,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D223" s="18" t="inlineStr">
+      <c r="D223" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22437,7 +22455,7 @@
       <c r="G223" s="21" t="n">
         <v>0.0016</v>
       </c>
-      <c r="H223" s="18" t="inlineStr">
+      <c r="H223" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -22495,7 +22513,7 @@
           <t>Components.StarTrackerZUnit</t>
         </is>
       </c>
-      <c r="D224" s="25" t="inlineStr">
+      <c r="D224" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22513,7 +22531,7 @@
       <c r="G224" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="H224" s="25" t="inlineStr">
+      <c r="H224" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -22571,7 +22589,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D225" s="18" t="inlineStr">
+      <c r="D225" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -22589,7 +22607,7 @@
       <c r="G225" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="H225" s="18" t="inlineStr">
+      <c r="H225" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -22643,7 +22661,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D226" s="25" t="inlineStr">
+      <c r="D226" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -22661,7 +22679,7 @@
       <c r="G226" s="21" t="n">
         <v>240</v>
       </c>
-      <c r="H226" s="25" t="inlineStr">
+      <c r="H226" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -22715,7 +22733,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D227" s="18" t="inlineStr">
+      <c r="D227" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -22733,7 +22751,7 @@
       <c r="G227" s="21" t="n">
         <v>0.26</v>
       </c>
-      <c r="H227" s="18" t="inlineStr">
+      <c r="H227" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -22787,7 +22805,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D228" s="25" t="inlineStr">
+      <c r="D228" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22805,7 +22823,7 @@
       <c r="G228" s="21" t="n">
         <v>0.68</v>
       </c>
-      <c r="H228" s="25" t="inlineStr">
+      <c r="H228" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -22863,7 +22881,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D229" s="18" t="inlineStr">
+      <c r="D229" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22881,7 +22899,7 @@
       <c r="G229" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H229" s="18" t="inlineStr">
+      <c r="H229" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -22939,7 +22957,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D230" s="25" t="inlineStr">
+      <c r="D230" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -22957,7 +22975,7 @@
       <c r="G230" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H230" s="25" t="inlineStr">
+      <c r="H230" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -23015,7 +23033,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D231" s="18" t="inlineStr">
+      <c r="D231" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23033,7 +23051,7 @@
       <c r="G231" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H231" s="18" t="inlineStr">
+      <c r="H231" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -23091,7 +23109,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D232" s="25" t="inlineStr">
+      <c r="D232" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23109,7 +23127,7 @@
       <c r="G232" s="21" t="n">
         <v>0.0022</v>
       </c>
-      <c r="H232" s="25" t="inlineStr">
+      <c r="H232" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -23167,7 +23185,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D233" s="18" t="inlineStr">
+      <c r="D233" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23185,7 +23203,7 @@
       <c r="G233" s="21" t="n">
         <v>0.0022</v>
       </c>
-      <c r="H233" s="18" t="inlineStr">
+      <c r="H233" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -23243,7 +23261,7 @@
           <t>Components.RateGyroUnit</t>
         </is>
       </c>
-      <c r="D234" s="25" t="inlineStr">
+      <c r="D234" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23261,7 +23279,7 @@
       <c r="G234" s="21" t="n">
         <v>0.0022</v>
       </c>
-      <c r="H234" s="25" t="inlineStr">
+      <c r="H234" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -23319,7 +23337,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D235" s="18" t="inlineStr">
+      <c r="D235" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -23337,7 +23355,7 @@
       <c r="G235" s="21" t="n">
         <v>84.59999999999999</v>
       </c>
-      <c r="H235" s="18" t="inlineStr">
+      <c r="H235" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -23391,7 +23409,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D236" s="25" t="inlineStr">
+      <c r="D236" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -23409,7 +23427,7 @@
       <c r="G236" s="21" t="n">
         <v>85</v>
       </c>
-      <c r="H236" s="25" t="inlineStr">
+      <c r="H236" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -23463,7 +23481,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D237" s="18" t="inlineStr">
+      <c r="D237" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -23481,7 +23499,7 @@
       <c r="G237" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="H237" s="18" t="inlineStr">
+      <c r="H237" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -23535,7 +23553,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D238" s="25" t="inlineStr">
+      <c r="D238" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23553,7 +23571,7 @@
       <c r="G238" s="21" t="n">
         <v>0.19</v>
       </c>
-      <c r="H238" s="25" t="inlineStr">
+      <c r="H238" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -23611,7 +23629,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D239" s="18" t="inlineStr">
+      <c r="D239" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23629,7 +23647,7 @@
       <c r="G239" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H239" s="18" t="inlineStr">
+      <c r="H239" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -23687,7 +23705,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D240" s="25" t="inlineStr">
+      <c r="D240" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23705,7 +23723,7 @@
       <c r="G240" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H240" s="25" t="inlineStr">
+      <c r="H240" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -23763,7 +23781,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D241" s="18" t="inlineStr">
+      <c r="D241" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23781,7 +23799,7 @@
       <c r="G241" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H241" s="18" t="inlineStr">
+      <c r="H241" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -23839,7 +23857,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D242" s="25" t="inlineStr">
+      <c r="D242" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23857,7 +23875,7 @@
       <c r="G242" s="21" t="n">
         <v>0.00025</v>
       </c>
-      <c r="H242" s="25" t="inlineStr">
+      <c r="H242" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -23915,7 +23933,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D243" s="18" t="inlineStr">
+      <c r="D243" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -23933,7 +23951,7 @@
       <c r="G243" s="21" t="n">
         <v>0.00022</v>
       </c>
-      <c r="H243" s="18" t="inlineStr">
+      <c r="H243" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -23991,7 +24009,7 @@
           <t>Components.MEMSIMUUnit</t>
         </is>
       </c>
-      <c r="D244" s="25" t="inlineStr">
+      <c r="D244" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24009,7 +24027,7 @@
       <c r="G244" s="21" t="n">
         <v>0.00024</v>
       </c>
-      <c r="H244" s="25" t="inlineStr">
+      <c r="H244" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -24067,7 +24085,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D245" s="18" t="inlineStr">
+      <c r="D245" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -24085,7 +24103,7 @@
       <c r="G245" s="21" t="n">
         <v>129.8</v>
       </c>
-      <c r="H245" s="18" t="inlineStr">
+      <c r="H245" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -24139,7 +24157,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D246" s="25" t="inlineStr">
+      <c r="D246" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -24157,7 +24175,7 @@
       <c r="G246" s="21" t="n">
         <v>62</v>
       </c>
-      <c r="H246" s="25" t="inlineStr">
+      <c r="H246" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -24211,7 +24229,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D247" s="18" t="inlineStr">
+      <c r="D247" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -24229,7 +24247,7 @@
       <c r="G247" s="21" t="n">
         <v>0.08</v>
       </c>
-      <c r="H247" s="18" t="inlineStr">
+      <c r="H247" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -24283,7 +24301,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D248" s="25" t="inlineStr">
+      <c r="D248" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24301,7 +24319,7 @@
       <c r="G248" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H248" s="25" t="inlineStr">
+      <c r="H248" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -24359,7 +24377,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D249" s="18" t="inlineStr">
+      <c r="D249" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24377,7 +24395,7 @@
       <c r="G249" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="H249" s="18" t="inlineStr">
+      <c r="H249" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -24435,7 +24453,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D250" s="25" t="inlineStr">
+      <c r="D250" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24453,7 +24471,7 @@
       <c r="G250" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H250" s="25" t="inlineStr">
+      <c r="H250" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -24511,7 +24529,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D251" s="18" t="inlineStr">
+      <c r="D251" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24529,7 +24547,7 @@
       <c r="G251" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H251" s="18" t="inlineStr">
+      <c r="H251" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -24587,7 +24605,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D252" s="25" t="inlineStr">
+      <c r="D252" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24605,7 +24623,7 @@
       <c r="G252" s="21" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H252" s="25" t="inlineStr">
+      <c r="H252" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -24663,7 +24681,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D253" s="18" t="inlineStr">
+      <c r="D253" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24681,7 +24699,7 @@
       <c r="G253" s="21" t="n">
         <v>0.0011</v>
       </c>
-      <c r="H253" s="18" t="inlineStr">
+      <c r="H253" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -24739,7 +24757,7 @@
           <t>Components.MagnetometerUnit</t>
         </is>
       </c>
-      <c r="D254" s="25" t="inlineStr">
+      <c r="D254" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -24757,7 +24775,7 @@
       <c r="G254" s="21" t="n">
         <v>0.0011</v>
       </c>
-      <c r="H254" s="25" t="inlineStr">
+      <c r="H254" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -24815,7 +24833,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D255" s="18" t="inlineStr">
+      <c r="D255" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -24833,7 +24851,7 @@
       <c r="G255" s="21" t="n">
         <v>157.3</v>
       </c>
-      <c r="H255" s="18" t="inlineStr">
+      <c r="H255" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -24887,7 +24905,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D256" s="25" t="inlineStr">
+      <c r="D256" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -24905,7 +24923,7 @@
       <c r="G256" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="H256" s="25" t="inlineStr">
+      <c r="H256" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -24959,7 +24977,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D257" s="18" t="inlineStr">
+      <c r="D257" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -24977,7 +24995,7 @@
       <c r="G257" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H257" s="18" t="inlineStr">
+      <c r="H257" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -25031,7 +25049,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D258" s="25" t="inlineStr">
+      <c r="D258" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25049,7 +25067,7 @@
       <c r="G258" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="H258" s="25" t="inlineStr">
+      <c r="H258" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -25107,7 +25125,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D259" s="18" t="inlineStr">
+      <c r="D259" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25125,7 +25143,7 @@
       <c r="G259" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H259" s="18" t="inlineStr">
+      <c r="H259" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -25183,7 +25201,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D260" s="25" t="inlineStr">
+      <c r="D260" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25201,7 +25219,7 @@
       <c r="G260" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="H260" s="25" t="inlineStr">
+      <c r="H260" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -25259,7 +25277,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D261" s="18" t="inlineStr">
+      <c r="D261" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25277,7 +25295,7 @@
       <c r="G261" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H261" s="18" t="inlineStr">
+      <c r="H261" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -25335,7 +25353,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D262" s="25" t="inlineStr">
+      <c r="D262" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25353,7 +25371,7 @@
       <c r="G262" s="21" t="n">
         <v>0.00015</v>
       </c>
-      <c r="H262" s="25" t="inlineStr">
+      <c r="H262" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -25411,7 +25429,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D263" s="18" t="inlineStr">
+      <c r="D263" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25429,7 +25447,7 @@
       <c r="G263" s="21" t="n">
         <v>0.0001</v>
       </c>
-      <c r="H263" s="18" t="inlineStr">
+      <c r="H263" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -25487,7 +25505,7 @@
           <t>Components.SunSensorUnit</t>
         </is>
       </c>
-      <c r="D264" s="25" t="inlineStr">
+      <c r="D264" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -25505,7 +25523,7 @@
       <c r="G264" s="21" t="n">
         <v>0.00015</v>
       </c>
-      <c r="H264" s="25" t="inlineStr">
+      <c r="H264" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -25563,7 +25581,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D265" s="18" t="inlineStr">
+      <c r="D265" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -25581,7 +25599,7 @@
       <c r="G265" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="H265" s="18" t="inlineStr">
+      <c r="H265" s="62" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25639,7 +25657,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D266" s="25" t="inlineStr">
+      <c r="D266" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -25657,7 +25675,7 @@
       <c r="G266" s="21" t="n">
         <v>3.571428571</v>
       </c>
-      <c r="H266" s="25" t="inlineStr">
+      <c r="H266" s="63" t="inlineStr">
         <is>
           <t>A·m²/A</t>
         </is>
@@ -25711,7 +25729,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D267" s="18" t="inlineStr">
+      <c r="D267" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -25729,7 +25747,7 @@
       <c r="G267" s="21" t="n">
         <v>3.571428571</v>
       </c>
-      <c r="H267" s="18" t="inlineStr">
+      <c r="H267" s="62" t="inlineStr">
         <is>
           <t>A·m²/A</t>
         </is>
@@ -25783,7 +25801,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D268" s="25" t="inlineStr">
+      <c r="D268" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -25801,7 +25819,7 @@
       <c r="G268" s="21" t="n">
         <v>3.571428571</v>
       </c>
-      <c r="H268" s="25" t="inlineStr">
+      <c r="H268" s="63" t="inlineStr">
         <is>
           <t>A·m²/A</t>
         </is>
@@ -25855,7 +25873,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D269" s="18" t="inlineStr">
+      <c r="D269" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -25873,7 +25891,7 @@
       <c r="G269" s="21" t="n">
         <v>190</v>
       </c>
-      <c r="H269" s="18" t="inlineStr">
+      <c r="H269" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -25927,7 +25945,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D270" s="25" t="inlineStr">
+      <c r="D270" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -25945,7 +25963,7 @@
       <c r="G270" s="21" t="n">
         <v>0.32</v>
       </c>
-      <c r="H270" s="25" t="inlineStr">
+      <c r="H270" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -25999,7 +26017,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D271" s="18" t="inlineStr">
+      <c r="D271" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26017,7 +26035,7 @@
       <c r="G271" s="21" t="n">
         <v>0.42</v>
       </c>
-      <c r="H271" s="18" t="inlineStr">
+      <c r="H271" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -26075,7 +26093,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D272" s="25" t="inlineStr">
+      <c r="D272" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26093,7 +26111,7 @@
       <c r="G272" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H272" s="25" t="inlineStr">
+      <c r="H272" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -26151,7 +26169,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D273" s="18" t="inlineStr">
+      <c r="D273" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26169,7 +26187,7 @@
       <c r="G273" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H273" s="18" t="inlineStr">
+      <c r="H273" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -26227,7 +26245,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D274" s="25" t="inlineStr">
+      <c r="D274" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26245,7 +26263,7 @@
       <c r="G274" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H274" s="25" t="inlineStr">
+      <c r="H274" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -26303,7 +26321,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D275" s="18" t="inlineStr">
+      <c r="D275" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26321,7 +26339,7 @@
       <c r="G275" s="21" t="n">
         <v>0.003</v>
       </c>
-      <c r="H275" s="18" t="inlineStr">
+      <c r="H275" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -26379,7 +26397,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D276" s="25" t="inlineStr">
+      <c r="D276" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26397,7 +26415,7 @@
       <c r="G276" s="21" t="n">
         <v>0.003</v>
       </c>
-      <c r="H276" s="25" t="inlineStr">
+      <c r="H276" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -26455,7 +26473,7 @@
           <t>Components.MagnetorquerUnit</t>
         </is>
       </c>
-      <c r="D277" s="18" t="inlineStr">
+      <c r="D277" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -26473,7 +26491,7 @@
       <c r="G277" s="21" t="n">
         <v>0.003</v>
       </c>
-      <c r="H277" s="18" t="inlineStr">
+      <c r="H277" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -26603,7 +26621,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D279" s="18" t="inlineStr">
+      <c r="D279" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -26621,7 +26639,7 @@
       <c r="G279" s="21" t="n">
         <v>100000000</v>
       </c>
-      <c r="H279" s="18" t="inlineStr">
+      <c r="H279" s="62" t="inlineStr">
         <is>
           <t>byte</t>
         </is>
@@ -26675,7 +26693,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D280" s="25" t="inlineStr">
+      <c r="D280" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -26693,7 +26711,7 @@
       <c r="G280" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="H280" s="25" t="inlineStr">
+      <c r="H280" s="63" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -26751,7 +26769,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D281" s="18" t="inlineStr">
+      <c r="D281" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -26769,7 +26787,7 @@
       <c r="G281" s="21" t="n">
         <v>8.5</v>
       </c>
-      <c r="H281" s="18" t="inlineStr">
+      <c r="H281" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -26823,7 +26841,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D282" s="25" t="inlineStr">
+      <c r="D282" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -26841,7 +26859,7 @@
       <c r="G282" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="H282" s="25" t="inlineStr">
+      <c r="H282" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -26899,7 +26917,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D283" s="18" t="inlineStr">
+      <c r="D283" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -26917,7 +26935,7 @@
       <c r="G283" s="21" t="n">
         <v>2420</v>
       </c>
-      <c r="H283" s="18" t="inlineStr">
+      <c r="H283" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -26971,7 +26989,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D284" s="25" t="inlineStr">
+      <c r="D284" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -26989,7 +27007,7 @@
       <c r="G284" s="21" t="n">
         <v>390</v>
       </c>
-      <c r="H284" s="25" t="inlineStr">
+      <c r="H284" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -27043,7 +27061,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D285" s="18" t="inlineStr">
+      <c r="D285" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -27061,7 +27079,7 @@
       <c r="G285" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="H285" s="18" t="inlineStr">
+      <c r="H285" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -27115,7 +27133,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D286" s="25" t="inlineStr">
+      <c r="D286" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -27133,7 +27151,7 @@
       <c r="G286" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H286" s="25" t="inlineStr">
+      <c r="H286" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -27187,7 +27205,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D287" s="18" t="inlineStr">
+      <c r="D287" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -27205,7 +27223,7 @@
       <c r="G287" s="21" t="n">
         <v>0.25</v>
       </c>
-      <c r="H287" s="18" t="inlineStr">
+      <c r="H287" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -27259,7 +27277,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D288" s="25" t="inlineStr">
+      <c r="D288" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27277,7 +27295,7 @@
       <c r="G288" s="21" t="n">
         <v>3.85</v>
       </c>
-      <c r="H288" s="25" t="inlineStr">
+      <c r="H288" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -27335,7 +27353,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D289" s="18" t="inlineStr">
+      <c r="D289" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27353,7 +27371,7 @@
       <c r="G289" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H289" s="18" t="inlineStr">
+      <c r="H289" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -27411,7 +27429,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D290" s="25" t="inlineStr">
+      <c r="D290" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27429,7 +27447,7 @@
       <c r="G290" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H290" s="25" t="inlineStr">
+      <c r="H290" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -27487,7 +27505,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D291" s="18" t="inlineStr">
+      <c r="D291" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27505,7 +27523,7 @@
       <c r="G291" s="21" t="n">
         <v>0.18</v>
       </c>
-      <c r="H291" s="18" t="inlineStr">
+      <c r="H291" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -27563,7 +27581,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D292" s="25" t="inlineStr">
+      <c r="D292" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27581,7 +27599,7 @@
       <c r="G292" s="21" t="n">
         <v>0.11</v>
       </c>
-      <c r="H292" s="25" t="inlineStr">
+      <c r="H292" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -27639,7 +27657,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D293" s="18" t="inlineStr">
+      <c r="D293" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27657,7 +27675,7 @@
       <c r="G293" s="21" t="n">
         <v>0.1</v>
       </c>
-      <c r="H293" s="18" t="inlineStr">
+      <c r="H293" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -27715,7 +27733,7 @@
           <t>Components.EarthObservationCameraUnit</t>
         </is>
       </c>
-      <c r="D294" s="25" t="inlineStr">
+      <c r="D294" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -27733,7 +27751,7 @@
       <c r="G294" s="21" t="n">
         <v>0.045</v>
       </c>
-      <c r="H294" s="25" t="inlineStr">
+      <c r="H294" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -27791,7 +27809,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D295" s="18" t="inlineStr">
+      <c r="D295" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -27809,7 +27827,7 @@
       <c r="G295" s="21" t="n">
         <v>2000000</v>
       </c>
-      <c r="H295" s="18" t="inlineStr">
+      <c r="H295" s="62" t="inlineStr">
         <is>
           <t>byte/s</t>
         </is>
@@ -27863,7 +27881,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D296" s="25" t="inlineStr">
+      <c r="D296" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -27881,7 +27899,7 @@
       <c r="G296" s="21" t="n">
         <v>64.90000000000001</v>
       </c>
-      <c r="H296" s="25" t="inlineStr">
+      <c r="H296" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -27935,7 +27953,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D297" s="18" t="inlineStr">
+      <c r="D297" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -27953,7 +27971,7 @@
       <c r="G297" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="H297" s="18" t="inlineStr">
+      <c r="H297" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -28007,7 +28025,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D298" s="25" t="inlineStr">
+      <c r="D298" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -28025,7 +28043,7 @@
       <c r="G298" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="H298" s="25" t="inlineStr">
+      <c r="H298" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -28079,7 +28097,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D299" s="18" t="inlineStr">
+      <c r="D299" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28097,7 +28115,7 @@
       <c r="G299" s="21" t="n">
         <v>0.16</v>
       </c>
-      <c r="H299" s="18" t="inlineStr">
+      <c r="H299" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -28155,7 +28173,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D300" s="25" t="inlineStr">
+      <c r="D300" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28173,7 +28191,7 @@
       <c r="G300" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H300" s="25" t="inlineStr">
+      <c r="H300" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -28231,7 +28249,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D301" s="18" t="inlineStr">
+      <c r="D301" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28249,7 +28267,7 @@
       <c r="G301" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H301" s="18" t="inlineStr">
+      <c r="H301" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -28307,7 +28325,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D302" s="25" t="inlineStr">
+      <c r="D302" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28325,7 +28343,7 @@
       <c r="G302" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H302" s="25" t="inlineStr">
+      <c r="H302" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -28383,7 +28401,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D303" s="18" t="inlineStr">
+      <c r="D303" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28401,7 +28419,7 @@
       <c r="G303" s="21" t="n">
         <v>0.00025</v>
       </c>
-      <c r="H303" s="18" t="inlineStr">
+      <c r="H303" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -28459,7 +28477,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D304" s="25" t="inlineStr">
+      <c r="D304" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28477,7 +28495,7 @@
       <c r="G304" s="21" t="n">
         <v>0.0003</v>
       </c>
-      <c r="H304" s="25" t="inlineStr">
+      <c r="H304" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -28535,7 +28553,7 @@
           <t>Components.SelfieCameraUnit</t>
         </is>
       </c>
-      <c r="D305" s="18" t="inlineStr">
+      <c r="D305" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28553,7 +28571,7 @@
       <c r="G305" s="21" t="n">
         <v>0.0002</v>
       </c>
-      <c r="H305" s="18" t="inlineStr">
+      <c r="H305" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -28611,7 +28629,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D306" s="25" t="inlineStr">
+      <c r="D306" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -28629,7 +28647,7 @@
       <c r="G306" s="21" t="n">
         <v>51.9</v>
       </c>
-      <c r="H306" s="25" t="inlineStr">
+      <c r="H306" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -28683,7 +28701,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D307" s="18" t="inlineStr">
+      <c r="D307" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -28701,7 +28719,7 @@
       <c r="G307" s="21" t="n">
         <v>5250</v>
       </c>
-      <c r="H307" s="18" t="inlineStr">
+      <c r="H307" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -28759,7 +28777,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D308" s="25" t="inlineStr">
+      <c r="D308" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -28777,7 +28795,7 @@
       <c r="G308" s="21" t="n">
         <v>160</v>
       </c>
-      <c r="H308" s="25" t="inlineStr">
+      <c r="H308" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -28831,7 +28849,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D309" s="18" t="inlineStr">
+      <c r="D309" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -28849,7 +28867,7 @@
       <c r="G309" s="21" t="n">
         <v>0.34</v>
       </c>
-      <c r="H309" s="18" t="inlineStr">
+      <c r="H309" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -28903,7 +28921,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D310" s="25" t="inlineStr">
+      <c r="D310" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28921,7 +28939,7 @@
       <c r="G310" s="21" t="n">
         <v>0.28</v>
       </c>
-      <c r="H310" s="25" t="inlineStr">
+      <c r="H310" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -28979,7 +28997,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D311" s="18" t="inlineStr">
+      <c r="D311" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -28997,7 +29015,7 @@
       <c r="G311" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H311" s="18" t="inlineStr">
+      <c r="H311" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -29055,7 +29073,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D312" s="25" t="inlineStr">
+      <c r="D312" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29073,7 +29091,7 @@
       <c r="G312" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H312" s="25" t="inlineStr">
+      <c r="H312" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -29131,7 +29149,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D313" s="18" t="inlineStr">
+      <c r="D313" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29149,7 +29167,7 @@
       <c r="G313" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H313" s="18" t="inlineStr">
+      <c r="H313" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -29207,7 +29225,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D314" s="25" t="inlineStr">
+      <c r="D314" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29225,7 +29243,7 @@
       <c r="G314" s="21" t="n">
         <v>0.0007</v>
       </c>
-      <c r="H314" s="25" t="inlineStr">
+      <c r="H314" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -29283,7 +29301,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D315" s="18" t="inlineStr">
+      <c r="D315" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29301,7 +29319,7 @@
       <c r="G315" s="21" t="n">
         <v>0.0009</v>
       </c>
-      <c r="H315" s="18" t="inlineStr">
+      <c r="H315" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -29359,7 +29377,7 @@
           <t>Components.NaviEnhancePayloadUnit</t>
         </is>
       </c>
-      <c r="D316" s="25" t="inlineStr">
+      <c r="D316" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29377,7 +29395,7 @@
       <c r="G316" s="21" t="n">
         <v>0.0007</v>
       </c>
-      <c r="H316" s="25" t="inlineStr">
+      <c r="H316" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -29435,7 +29453,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D317" s="18" t="inlineStr">
+      <c r="D317" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -29453,7 +29471,7 @@
       <c r="G317" s="21" t="n">
         <v>51.9</v>
       </c>
-      <c r="H317" s="18" t="inlineStr">
+      <c r="H317" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -29507,7 +29525,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D318" s="25" t="inlineStr">
+      <c r="D318" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -29525,7 +29543,7 @@
       <c r="G318" s="21" t="n">
         <v>1312.5</v>
       </c>
-      <c r="H318" s="25" t="inlineStr">
+      <c r="H318" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -29579,7 +29597,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D319" s="18" t="inlineStr">
+      <c r="D319" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -29597,7 +29615,7 @@
       <c r="G319" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H319" s="18" t="inlineStr">
+      <c r="H319" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -29651,7 +29669,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D320" s="25" t="inlineStr">
+      <c r="D320" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -29669,7 +29687,7 @@
       <c r="G320" s="21" t="n">
         <v>120</v>
       </c>
-      <c r="H320" s="25" t="inlineStr">
+      <c r="H320" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -29723,7 +29741,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D321" s="18" t="inlineStr">
+      <c r="D321" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -29741,7 +29759,7 @@
       <c r="G321" s="21" t="n">
         <v>3.2</v>
       </c>
-      <c r="H321" s="18" t="inlineStr">
+      <c r="H321" s="62" t="inlineStr">
         <is>
           <t>K/W</t>
         </is>
@@ -29795,7 +29813,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D322" s="25" t="inlineStr">
+      <c r="D322" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29813,7 +29831,7 @@
       <c r="G322" s="21" t="n">
         <v>0.22</v>
       </c>
-      <c r="H322" s="25" t="inlineStr">
+      <c r="H322" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -29871,7 +29889,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D323" s="18" t="inlineStr">
+      <c r="D323" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29889,7 +29907,7 @@
       <c r="G323" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H323" s="18" t="inlineStr">
+      <c r="H323" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -29947,7 +29965,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D324" s="25" t="inlineStr">
+      <c r="D324" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -29965,7 +29983,7 @@
       <c r="G324" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H324" s="25" t="inlineStr">
+      <c r="H324" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -30023,7 +30041,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D325" s="18" t="inlineStr">
+      <c r="D325" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30041,7 +30059,7 @@
       <c r="G325" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H325" s="18" t="inlineStr">
+      <c r="H325" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -30099,7 +30117,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D326" s="25" t="inlineStr">
+      <c r="D326" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30117,7 +30135,7 @@
       <c r="G326" s="21" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H326" s="25" t="inlineStr">
+      <c r="H326" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -30175,7 +30193,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D327" s="18" t="inlineStr">
+      <c r="D327" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30193,7 +30211,7 @@
       <c r="G327" s="21" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="H327" s="18" t="inlineStr">
+      <c r="H327" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -30251,7 +30269,7 @@
           <t>Components.SpaceTimePayloadUnit</t>
         </is>
       </c>
-      <c r="D328" s="25" t="inlineStr">
+      <c r="D328" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30269,7 +30287,7 @@
       <c r="G328" s="21" t="n">
         <v>0.0005</v>
       </c>
-      <c r="H328" s="25" t="inlineStr">
+      <c r="H328" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -30327,7 +30345,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D329" s="18" t="inlineStr">
+      <c r="D329" s="62" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
@@ -30345,7 +30363,7 @@
       <c r="G329" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="H329" s="18" t="inlineStr">
+      <c r="H329" s="62" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -30403,7 +30421,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D330" s="25" t="inlineStr">
+      <c r="D330" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -30421,7 +30439,7 @@
       <c r="G330" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="H330" s="25" t="inlineStr">
+      <c r="H330" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -30475,7 +30493,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D331" s="18" t="inlineStr">
+      <c r="D331" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -30493,7 +30511,7 @@
       <c r="G331" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H331" s="18" t="inlineStr">
+      <c r="H331" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -30547,7 +30565,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D332" s="25" t="inlineStr">
+      <c r="D332" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -30565,7 +30583,7 @@
       <c r="G332" s="21" t="n">
         <v>420</v>
       </c>
-      <c r="H332" s="25" t="inlineStr">
+      <c r="H332" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -30619,7 +30637,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D333" s="18" t="inlineStr">
+      <c r="D333" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -30637,7 +30655,7 @@
       <c r="G333" s="21" t="n">
         <v>0.24</v>
       </c>
-      <c r="H333" s="18" t="inlineStr">
+      <c r="H333" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -30691,7 +30709,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D334" s="25" t="inlineStr">
+      <c r="D334" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30709,7 +30727,7 @@
       <c r="G334" s="21" t="n">
         <v>1.1</v>
       </c>
-      <c r="H334" s="25" t="inlineStr">
+      <c r="H334" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -30767,7 +30785,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D335" s="18" t="inlineStr">
+      <c r="D335" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30785,7 +30803,7 @@
       <c r="G335" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H335" s="18" t="inlineStr">
+      <c r="H335" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -30843,7 +30861,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D336" s="25" t="inlineStr">
+      <c r="D336" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30861,7 +30879,7 @@
       <c r="G336" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H336" s="25" t="inlineStr">
+      <c r="H336" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -30919,7 +30937,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D337" s="18" t="inlineStr">
+      <c r="D337" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -30937,7 +30955,7 @@
       <c r="G337" s="21" t="n">
         <v>-0.12</v>
       </c>
-      <c r="H337" s="18" t="inlineStr">
+      <c r="H337" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -30995,7 +31013,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D338" s="25" t="inlineStr">
+      <c r="D338" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31013,7 +31031,7 @@
       <c r="G338" s="21" t="n">
         <v>0.014</v>
       </c>
-      <c r="H338" s="25" t="inlineStr">
+      <c r="H338" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -31071,7 +31089,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D339" s="18" t="inlineStr">
+      <c r="D339" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31089,7 +31107,7 @@
       <c r="G339" s="21" t="n">
         <v>0.013</v>
       </c>
-      <c r="H339" s="18" t="inlineStr">
+      <c r="H339" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -31147,7 +31165,7 @@
           <t>Components.FotonAmurPayloadUnit</t>
         </is>
       </c>
-      <c r="D340" s="25" t="inlineStr">
+      <c r="D340" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31165,7 +31183,7 @@
       <c r="G340" s="21" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="H340" s="25" t="inlineStr">
+      <c r="H340" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -31295,7 +31313,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D342" s="25" t="inlineStr">
+      <c r="D342" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -31313,7 +31331,7 @@
       <c r="G342" s="21" t="n">
         <v>185</v>
       </c>
-      <c r="H342" s="25" t="inlineStr">
+      <c r="H342" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -31367,7 +31385,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D343" s="18" t="inlineStr">
+      <c r="D343" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -31385,7 +31403,7 @@
       <c r="G343" s="21" t="n">
         <v>260</v>
       </c>
-      <c r="H343" s="18" t="inlineStr">
+      <c r="H343" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -31439,7 +31457,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D344" s="25" t="inlineStr">
+      <c r="D344" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -31457,7 +31475,7 @@
       <c r="G344" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="H344" s="25" t="inlineStr">
+      <c r="H344" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -31511,7 +31529,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D345" s="18" t="inlineStr">
+      <c r="D345" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -31529,7 +31547,7 @@
       <c r="G345" s="21" t="n">
         <v>0.45</v>
       </c>
-      <c r="H345" s="18" t="inlineStr">
+      <c r="H345" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -31583,7 +31601,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D346" s="25" t="inlineStr">
+      <c r="D346" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31601,7 +31619,7 @@
       <c r="G346" s="21" t="n">
         <v>0.46</v>
       </c>
-      <c r="H346" s="25" t="inlineStr">
+      <c r="H346" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -31659,7 +31677,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D347" s="18" t="inlineStr">
+      <c r="D347" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31677,7 +31695,7 @@
       <c r="G347" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H347" s="18" t="inlineStr">
+      <c r="H347" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -31735,7 +31753,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D348" s="25" t="inlineStr">
+      <c r="D348" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31753,7 +31771,7 @@
       <c r="G348" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H348" s="25" t="inlineStr">
+      <c r="H348" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -31811,7 +31829,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D349" s="18" t="inlineStr">
+      <c r="D349" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31829,7 +31847,7 @@
       <c r="G349" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H349" s="18" t="inlineStr">
+      <c r="H349" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -31887,7 +31905,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D350" s="25" t="inlineStr">
+      <c r="D350" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31905,7 +31923,7 @@
       <c r="G350" s="21" t="n">
         <v>0.0012</v>
       </c>
-      <c r="H350" s="25" t="inlineStr">
+      <c r="H350" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -31963,7 +31981,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D351" s="18" t="inlineStr">
+      <c r="D351" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -31981,7 +31999,7 @@
       <c r="G351" s="21" t="n">
         <v>0.0015</v>
       </c>
-      <c r="H351" s="18" t="inlineStr">
+      <c r="H351" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -32039,7 +32057,7 @@
           <t>Components.OnboardComputerUnit</t>
         </is>
       </c>
-      <c r="D352" s="25" t="inlineStr">
+      <c r="D352" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32057,7 +32075,7 @@
       <c r="G352" s="21" t="n">
         <v>0.0011</v>
       </c>
-      <c r="H352" s="25" t="inlineStr">
+      <c r="H352" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -32115,7 +32133,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D353" s="18" t="inlineStr">
+      <c r="D353" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -32133,7 +32151,7 @@
       <c r="G353" s="21" t="n">
         <v>128000000000</v>
       </c>
-      <c r="H353" s="18" t="inlineStr">
+      <c r="H353" s="62" t="inlineStr">
         <is>
           <t>byte</t>
         </is>
@@ -32191,7 +32209,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D354" s="25" t="inlineStr">
+      <c r="D354" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -32209,7 +32227,7 @@
       <c r="G354" s="21" t="n">
         <v>51.9</v>
       </c>
-      <c r="H354" s="25" t="inlineStr">
+      <c r="H354" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -32263,7 +32281,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D355" s="18" t="inlineStr">
+      <c r="D355" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -32281,7 +32299,7 @@
       <c r="G355" s="21" t="n">
         <v>230</v>
       </c>
-      <c r="H355" s="18" t="inlineStr">
+      <c r="H355" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -32335,7 +32353,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D356" s="25" t="inlineStr">
+      <c r="D356" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -32353,7 +32371,7 @@
       <c r="G356" s="21" t="n">
         <v>0.42</v>
       </c>
-      <c r="H356" s="25" t="inlineStr">
+      <c r="H356" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -32407,7 +32425,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D357" s="18" t="inlineStr">
+      <c r="D357" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32425,7 +32443,7 @@
       <c r="G357" s="21" t="n">
         <v>0.44</v>
       </c>
-      <c r="H357" s="18" t="inlineStr">
+      <c r="H357" s="62" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -32483,7 +32501,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D358" s="25" t="inlineStr">
+      <c r="D358" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32501,7 +32519,7 @@
       <c r="G358" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H358" s="25" t="inlineStr">
+      <c r="H358" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -32559,7 +32577,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D359" s="18" t="inlineStr">
+      <c r="D359" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32577,7 +32595,7 @@
       <c r="G359" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H359" s="18" t="inlineStr">
+      <c r="H359" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -32635,7 +32653,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D360" s="25" t="inlineStr">
+      <c r="D360" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32653,7 +32671,7 @@
       <c r="G360" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H360" s="25" t="inlineStr">
+      <c r="H360" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -32711,7 +32729,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D361" s="18" t="inlineStr">
+      <c r="D361" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32729,7 +32747,7 @@
       <c r="G361" s="21" t="n">
         <v>0.0013</v>
       </c>
-      <c r="H361" s="18" t="inlineStr">
+      <c r="H361" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -32787,7 +32805,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D362" s="25" t="inlineStr">
+      <c r="D362" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32805,7 +32823,7 @@
       <c r="G362" s="21" t="n">
         <v>0.0017</v>
       </c>
-      <c r="H362" s="25" t="inlineStr">
+      <c r="H362" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -32863,7 +32881,7 @@
           <t>Components.DataRecorderUnit</t>
         </is>
       </c>
-      <c r="D363" s="18" t="inlineStr">
+      <c r="D363" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -32881,7 +32899,7 @@
       <c r="G363" s="21" t="n">
         <v>0.0012</v>
       </c>
-      <c r="H363" s="18" t="inlineStr">
+      <c r="H363" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -33011,7 +33029,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D365" s="18" t="inlineStr">
+      <c r="D365" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -33029,7 +33047,7 @@
       <c r="G365" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H365" s="18" t="inlineStr">
+      <c r="H365" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -33083,7 +33101,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D366" s="25" t="inlineStr">
+      <c r="D366" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -33101,7 +33119,7 @@
       <c r="G366" s="21" t="n">
         <v>165</v>
       </c>
-      <c r="H366" s="25" t="inlineStr">
+      <c r="H366" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -33155,7 +33173,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D367" s="18" t="inlineStr">
+      <c r="D367" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -33173,7 +33191,7 @@
       <c r="G367" s="21" t="n">
         <v>0.36</v>
       </c>
-      <c r="H367" s="18" t="inlineStr">
+      <c r="H367" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -33227,7 +33245,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D368" s="25" t="inlineStr">
+      <c r="D368" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33245,7 +33263,7 @@
       <c r="G368" s="21" t="n">
         <v>0.38</v>
       </c>
-      <c r="H368" s="25" t="inlineStr">
+      <c r="H368" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -33303,7 +33321,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D369" s="18" t="inlineStr">
+      <c r="D369" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33321,7 +33339,7 @@
       <c r="G369" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H369" s="18" t="inlineStr">
+      <c r="H369" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -33379,7 +33397,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D370" s="25" t="inlineStr">
+      <c r="D370" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33397,7 +33415,7 @@
       <c r="G370" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H370" s="25" t="inlineStr">
+      <c r="H370" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -33455,7 +33473,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D371" s="18" t="inlineStr">
+      <c r="D371" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33473,7 +33491,7 @@
       <c r="G371" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H371" s="18" t="inlineStr">
+      <c r="H371" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -33531,7 +33549,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D372" s="25" t="inlineStr">
+      <c r="D372" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33549,7 +33567,7 @@
       <c r="G372" s="21" t="n">
         <v>0.0011</v>
       </c>
-      <c r="H372" s="25" t="inlineStr">
+      <c r="H372" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -33607,7 +33625,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D373" s="18" t="inlineStr">
+      <c r="D373" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33625,7 +33643,7 @@
       <c r="G373" s="21" t="n">
         <v>0.0014</v>
       </c>
-      <c r="H373" s="18" t="inlineStr">
+      <c r="H373" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -33683,7 +33701,7 @@
           <t>Components.RadioReceiverUnit</t>
         </is>
       </c>
-      <c r="D374" s="25" t="inlineStr">
+      <c r="D374" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33701,7 +33719,7 @@
       <c r="G374" s="21" t="n">
         <v>0.001</v>
       </c>
-      <c r="H374" s="25" t="inlineStr">
+      <c r="H374" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -33759,7 +33777,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D375" s="18" t="inlineStr">
+      <c r="D375" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -33777,7 +33795,7 @@
       <c r="G375" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="H375" s="18" t="inlineStr">
+      <c r="H375" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -33831,7 +33849,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D376" s="25" t="inlineStr">
+      <c r="D376" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -33849,7 +33867,7 @@
       <c r="G376" s="21" t="n">
         <v>175</v>
       </c>
-      <c r="H376" s="25" t="inlineStr">
+      <c r="H376" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -33903,7 +33921,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D377" s="18" t="inlineStr">
+      <c r="D377" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -33921,7 +33939,7 @@
       <c r="G377" s="21" t="n">
         <v>0.4</v>
       </c>
-      <c r="H377" s="18" t="inlineStr">
+      <c r="H377" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -33975,7 +33993,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D378" s="25" t="inlineStr">
+      <c r="D378" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -33993,7 +34011,7 @@
       <c r="G378" s="21" t="n">
         <v>0.34</v>
       </c>
-      <c r="H378" s="25" t="inlineStr">
+      <c r="H378" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -34051,7 +34069,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D379" s="18" t="inlineStr">
+      <c r="D379" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -34069,7 +34087,7 @@
       <c r="G379" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H379" s="18" t="inlineStr">
+      <c r="H379" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -34127,7 +34145,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D380" s="25" t="inlineStr">
+      <c r="D380" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -34145,7 +34163,7 @@
       <c r="G380" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H380" s="25" t="inlineStr">
+      <c r="H380" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -34203,7 +34221,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D381" s="18" t="inlineStr">
+      <c r="D381" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -34221,7 +34239,7 @@
       <c r="G381" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H381" s="18" t="inlineStr">
+      <c r="H381" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -34279,7 +34297,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D382" s="25" t="inlineStr">
+      <c r="D382" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -34297,7 +34315,7 @@
       <c r="G382" s="21" t="n">
         <v>0.0009</v>
       </c>
-      <c r="H382" s="25" t="inlineStr">
+      <c r="H382" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -34355,7 +34373,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D383" s="18" t="inlineStr">
+      <c r="D383" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -34373,7 +34391,7 @@
       <c r="G383" s="21" t="n">
         <v>0.0012</v>
       </c>
-      <c r="H383" s="18" t="inlineStr">
+      <c r="H383" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -34431,7 +34449,7 @@
           <t>Components.LowRateTelemetryTransmitterUnit</t>
         </is>
       </c>
-      <c r="D384" s="25" t="inlineStr">
+      <c r="D384" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -34449,7 +34467,7 @@
       <c r="G384" s="21" t="n">
         <v>0.0009</v>
       </c>
-      <c r="H384" s="25" t="inlineStr">
+      <c r="H384" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -34507,7 +34525,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D385" s="18" t="inlineStr">
+      <c r="D385" s="62" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -34525,7 +34543,7 @@
       <c r="G385" s="21" t="n">
         <v>6250000</v>
       </c>
-      <c r="H385" s="18" t="inlineStr">
+      <c r="H385" s="62" t="inlineStr">
         <is>
           <t>byte/s</t>
         </is>
@@ -34579,7 +34597,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D386" s="25" t="inlineStr">
+      <c r="D386" s="63" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
@@ -34597,7 +34615,7 @@
       <c r="G386" s="21" t="n">
         <v>18750000</v>
       </c>
-      <c r="H386" s="25" t="inlineStr">
+      <c r="H386" s="63" t="inlineStr">
         <is>
           <t>byte/s</t>
         </is>
@@ -34651,7 +34669,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D387" s="18" t="inlineStr">
+      <c r="D387" s="62" t="inlineStr">
         <is>
           <t>Configuration</t>
         </is>
@@ -34669,7 +34687,7 @@
       <c r="G387" s="21" t="b">
         <v>0</v>
       </c>
-      <c r="H387" s="18" t="inlineStr">
+      <c r="H387" s="62" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -34727,7 +34745,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D388" s="25" t="inlineStr">
+      <c r="D388" s="63" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -34745,7 +34763,7 @@
       <c r="G388" s="21" t="n">
         <v>5.8</v>
       </c>
-      <c r="H388" s="25" t="inlineStr">
+      <c r="H388" s="63" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -34799,7 +34817,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D389" s="18" t="inlineStr">
+      <c r="D389" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -34817,7 +34835,7 @@
       <c r="G389" s="21" t="n">
         <v>0.05</v>
       </c>
-      <c r="H389" s="18" t="inlineStr">
+      <c r="H389" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -34871,7 +34889,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D390" s="25" t="inlineStr">
+      <c r="D390" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -34889,7 +34907,7 @@
       <c r="G390" s="21" t="n">
         <v>310</v>
       </c>
-      <c r="H390" s="25" t="inlineStr">
+      <c r="H390" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -34943,7 +34961,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D391" s="18" t="inlineStr">
+      <c r="D391" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -34961,7 +34979,7 @@
       <c r="G391" s="21" t="n">
         <v>0.65</v>
       </c>
-      <c r="H391" s="18" t="inlineStr">
+      <c r="H391" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -35015,7 +35033,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D392" s="25" t="inlineStr">
+      <c r="D392" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35033,7 +35051,7 @@
       <c r="G392" s="21" t="n">
         <v>0.62</v>
       </c>
-      <c r="H392" s="25" t="inlineStr">
+      <c r="H392" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -35091,7 +35109,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D393" s="18" t="inlineStr">
+      <c r="D393" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35109,7 +35127,7 @@
       <c r="G393" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H393" s="18" t="inlineStr">
+      <c r="H393" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -35167,7 +35185,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D394" s="25" t="inlineStr">
+      <c r="D394" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35185,7 +35203,7 @@
       <c r="G394" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H394" s="25" t="inlineStr">
+      <c r="H394" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -35243,7 +35261,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D395" s="18" t="inlineStr">
+      <c r="D395" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35261,7 +35279,7 @@
       <c r="G395" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H395" s="18" t="inlineStr">
+      <c r="H395" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -35319,7 +35337,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D396" s="25" t="inlineStr">
+      <c r="D396" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35337,7 +35355,7 @@
       <c r="G396" s="21" t="n">
         <v>0.002</v>
       </c>
-      <c r="H396" s="25" t="inlineStr">
+      <c r="H396" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -35395,7 +35413,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D397" s="18" t="inlineStr">
+      <c r="D397" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35413,7 +35431,7 @@
       <c r="G397" s="21" t="n">
         <v>0.0026</v>
       </c>
-      <c r="H397" s="18" t="inlineStr">
+      <c r="H397" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -35471,7 +35489,7 @@
           <t>Components.XBandTransmitterUnit</t>
         </is>
       </c>
-      <c r="D398" s="25" t="inlineStr">
+      <c r="D398" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35489,7 +35507,7 @@
       <c r="G398" s="21" t="n">
         <v>0.0018</v>
       </c>
-      <c r="H398" s="25" t="inlineStr">
+      <c r="H398" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -35547,7 +35565,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D399" s="18" t="inlineStr">
+      <c r="D399" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -35565,7 +35583,7 @@
       <c r="G399" s="21" t="n">
         <v>105</v>
       </c>
-      <c r="H399" s="18" t="inlineStr">
+      <c r="H399" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -35619,7 +35637,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D400" s="25" t="inlineStr">
+      <c r="D400" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -35637,7 +35655,7 @@
       <c r="G400" s="21" t="n">
         <v>0.14</v>
       </c>
-      <c r="H400" s="25" t="inlineStr">
+      <c r="H400" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -35691,7 +35709,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D401" s="18" t="inlineStr">
+      <c r="D401" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35709,7 +35727,7 @@
       <c r="G401" s="21" t="n">
         <v>0.22</v>
       </c>
-      <c r="H401" s="18" t="inlineStr">
+      <c r="H401" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -35767,7 +35785,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D402" s="25" t="inlineStr">
+      <c r="D402" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35785,7 +35803,7 @@
       <c r="G402" s="21" t="n">
         <v>0.24</v>
       </c>
-      <c r="H402" s="25" t="inlineStr">
+      <c r="H402" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -35843,7 +35861,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D403" s="18" t="inlineStr">
+      <c r="D403" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35861,7 +35879,7 @@
       <c r="G403" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H403" s="18" t="inlineStr">
+      <c r="H403" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -35919,7 +35937,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D404" s="25" t="inlineStr">
+      <c r="D404" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -35937,7 +35955,7 @@
       <c r="G404" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H404" s="25" t="inlineStr">
+      <c r="H404" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -35995,7 +36013,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D405" s="18" t="inlineStr">
+      <c r="D405" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36013,7 +36031,7 @@
       <c r="G405" s="21" t="n">
         <v>0.22</v>
       </c>
-      <c r="H405" s="18" t="inlineStr">
+      <c r="H405" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -36071,7 +36089,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D406" s="25" t="inlineStr">
+      <c r="D406" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36089,7 +36107,7 @@
       <c r="G406" s="21" t="n">
         <v>0.0028</v>
       </c>
-      <c r="H406" s="25" t="inlineStr">
+      <c r="H406" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -36147,7 +36165,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D407" s="18" t="inlineStr">
+      <c r="D407" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36165,7 +36183,7 @@
       <c r="G407" s="21" t="n">
         <v>0.0028</v>
       </c>
-      <c r="H407" s="18" t="inlineStr">
+      <c r="H407" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -36223,7 +36241,7 @@
           <t>Components.AntennaUnit</t>
         </is>
       </c>
-      <c r="D408" s="25" t="inlineStr">
+      <c r="D408" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36241,7 +36259,7 @@
       <c r="G408" s="21" t="n">
         <v>0.0004</v>
       </c>
-      <c r="H408" s="25" t="inlineStr">
+      <c r="H408" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -36375,7 +36393,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D410" s="25" t="inlineStr">
+      <c r="D410" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -36393,7 +36411,7 @@
       <c r="G410" s="21" t="n">
         <v>190</v>
       </c>
-      <c r="H410" s="25" t="inlineStr">
+      <c r="H410" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -36447,7 +36465,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D411" s="18" t="inlineStr">
+      <c r="D411" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -36465,7 +36483,7 @@
       <c r="G411" s="21" t="n">
         <v>0.35</v>
       </c>
-      <c r="H411" s="18" t="inlineStr">
+      <c r="H411" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -36519,7 +36537,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D412" s="25" t="inlineStr">
+      <c r="D412" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36537,7 +36555,7 @@
       <c r="G412" s="21" t="n">
         <v>0.31</v>
       </c>
-      <c r="H412" s="25" t="inlineStr">
+      <c r="H412" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -36595,7 +36613,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D413" s="18" t="inlineStr">
+      <c r="D413" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36613,7 +36631,7 @@
       <c r="G413" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H413" s="18" t="inlineStr">
+      <c r="H413" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -36671,7 +36689,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D414" s="25" t="inlineStr">
+      <c r="D414" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36689,7 +36707,7 @@
       <c r="G414" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H414" s="25" t="inlineStr">
+      <c r="H414" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -36747,7 +36765,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D415" s="18" t="inlineStr">
+      <c r="D415" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36765,7 +36783,7 @@
       <c r="G415" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H415" s="18" t="inlineStr">
+      <c r="H415" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -36823,7 +36841,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D416" s="25" t="inlineStr">
+      <c r="D416" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36841,7 +36859,7 @@
       <c r="G416" s="21" t="n">
         <v>0.0008</v>
       </c>
-      <c r="H416" s="25" t="inlineStr">
+      <c r="H416" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -36899,7 +36917,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D417" s="18" t="inlineStr">
+      <c r="D417" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36917,7 +36935,7 @@
       <c r="G417" s="21" t="n">
         <v>0.0011</v>
       </c>
-      <c r="H417" s="18" t="inlineStr">
+      <c r="H417" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -36975,7 +36993,7 @@
           <t>Components.GPSReceiverUnit</t>
         </is>
       </c>
-      <c r="D418" s="25" t="inlineStr">
+      <c r="D418" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -36993,7 +37011,7 @@
       <c r="G418" s="21" t="n">
         <v>0.0009</v>
       </c>
-      <c r="H418" s="25" t="inlineStr">
+      <c r="H418" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -37127,7 +37145,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D420" s="25" t="inlineStr">
+      <c r="D420" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -37145,7 +37163,7 @@
       <c r="G420" s="21" t="n">
         <v>270</v>
       </c>
-      <c r="H420" s="25" t="inlineStr">
+      <c r="H420" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -37199,7 +37217,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D421" s="18" t="inlineStr">
+      <c r="D421" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -37217,7 +37235,7 @@
       <c r="G421" s="21" t="n">
         <v>0.52</v>
       </c>
-      <c r="H421" s="18" t="inlineStr">
+      <c r="H421" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -37271,7 +37289,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D422" s="25" t="inlineStr">
+      <c r="D422" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37289,7 +37307,7 @@
       <c r="G422" s="21" t="n">
         <v>0.48</v>
       </c>
-      <c r="H422" s="25" t="inlineStr">
+      <c r="H422" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -37347,7 +37365,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D423" s="18" t="inlineStr">
+      <c r="D423" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37365,7 +37383,7 @@
       <c r="G423" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H423" s="18" t="inlineStr">
+      <c r="H423" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -37423,7 +37441,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D424" s="25" t="inlineStr">
+      <c r="D424" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37441,7 +37459,7 @@
       <c r="G424" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H424" s="25" t="inlineStr">
+      <c r="H424" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -37499,7 +37517,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D425" s="18" t="inlineStr">
+      <c r="D425" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37517,7 +37535,7 @@
       <c r="G425" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H425" s="18" t="inlineStr">
+      <c r="H425" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -37575,7 +37593,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D426" s="25" t="inlineStr">
+      <c r="D426" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37593,7 +37611,7 @@
       <c r="G426" s="21" t="n">
         <v>0.0014</v>
       </c>
-      <c r="H426" s="25" t="inlineStr">
+      <c r="H426" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -37651,7 +37669,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D427" s="18" t="inlineStr">
+      <c r="D427" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37669,7 +37687,7 @@
       <c r="G427" s="21" t="n">
         <v>0.0018</v>
       </c>
-      <c r="H427" s="18" t="inlineStr">
+      <c r="H427" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -37727,7 +37745,7 @@
           <t>Components.ThermalControllerUnit</t>
         </is>
       </c>
-      <c r="D428" s="25" t="inlineStr">
+      <c r="D428" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -37745,7 +37763,7 @@
       <c r="G428" s="21" t="n">
         <v>0.0013</v>
       </c>
-      <c r="H428" s="25" t="inlineStr">
+      <c r="H428" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -37803,7 +37821,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D429" s="18" t="inlineStr">
+      <c r="D429" s="62" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
@@ -37821,7 +37839,7 @@
       <c r="G429" s="21" t="n">
         <v>144</v>
       </c>
-      <c r="H429" s="18" t="inlineStr">
+      <c r="H429" s="62" t="inlineStr">
         <is>
           <t>Ω</t>
         </is>
@@ -37879,7 +37897,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D430" s="25" t="inlineStr">
+      <c r="D430" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -37897,7 +37915,7 @@
       <c r="G430" s="21" t="n">
         <v>560</v>
       </c>
-      <c r="H430" s="25" t="inlineStr">
+      <c r="H430" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -37951,7 +37969,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D431" s="18" t="inlineStr">
+      <c r="D431" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -37969,7 +37987,7 @@
       <c r="G431" s="21" t="n">
         <v>0.3</v>
       </c>
-      <c r="H431" s="18" t="inlineStr">
+      <c r="H431" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -38023,7 +38041,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D432" s="25" t="inlineStr">
+      <c r="D432" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38041,7 +38059,7 @@
       <c r="G432" s="21" t="n">
         <v>0.55</v>
       </c>
-      <c r="H432" s="25" t="inlineStr">
+      <c r="H432" s="63" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
@@ -38099,7 +38117,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D433" s="18" t="inlineStr">
+      <c r="D433" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38117,7 +38135,7 @@
       <c r="G433" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H433" s="18" t="inlineStr">
+      <c r="H433" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -38175,7 +38193,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D434" s="25" t="inlineStr">
+      <c r="D434" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38193,7 +38211,7 @@
       <c r="G434" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H434" s="25" t="inlineStr">
+      <c r="H434" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -38251,7 +38269,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D435" s="18" t="inlineStr">
+      <c r="D435" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38269,7 +38287,7 @@
       <c r="G435" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H435" s="18" t="inlineStr">
+      <c r="H435" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -38327,7 +38345,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D436" s="25" t="inlineStr">
+      <c r="D436" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38345,7 +38363,7 @@
       <c r="G436" s="21" t="n">
         <v>0.006</v>
       </c>
-      <c r="H436" s="25" t="inlineStr">
+      <c r="H436" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -38403,7 +38421,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D437" s="18" t="inlineStr">
+      <c r="D437" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38421,7 +38439,7 @@
       <c r="G437" s="21" t="n">
         <v>0.006</v>
       </c>
-      <c r="H437" s="18" t="inlineStr">
+      <c r="H437" s="62" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -38479,7 +38497,7 @@
           <t>Components.HeaterRadiatorUnit</t>
         </is>
       </c>
-      <c r="D438" s="25" t="inlineStr">
+      <c r="D438" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -38497,7 +38515,7 @@
       <c r="G438" s="21" t="n">
         <v>0.004</v>
       </c>
-      <c r="H438" s="25" t="inlineStr">
+      <c r="H438" s="63" t="inlineStr">
         <is>
           <t>kg·m²</t>
         </is>
@@ -38555,7 +38573,7 @@
           <t>Systems.Four_systems.ThermalOverall</t>
         </is>
       </c>
-      <c r="D439" s="18" t="inlineStr">
+      <c r="D439" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -38573,7 +38591,7 @@
       <c r="G439" s="21" t="n">
         <v>0.6</v>
       </c>
-      <c r="H439" s="18" t="inlineStr">
+      <c r="H439" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -38631,7 +38649,7 @@
           <t>Systems.Four_systems.ThermalOverall</t>
         </is>
       </c>
-      <c r="D440" s="25" t="inlineStr">
+      <c r="D440" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -38649,7 +38667,7 @@
       <c r="G440" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="H440" s="25" t="inlineStr">
+      <c r="H440" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -38707,7 +38725,7 @@
           <t>Systems.Four_systems.ThermalOverall</t>
         </is>
       </c>
-      <c r="D441" s="18" t="inlineStr">
+      <c r="D441" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -38725,7 +38743,7 @@
       <c r="G441" s="21" t="n">
         <v>0.8</v>
       </c>
-      <c r="H441" s="18" t="inlineStr">
+      <c r="H441" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -38783,7 +38801,7 @@
           <t>Systems.Four_systems.ThermalOverall</t>
         </is>
       </c>
-      <c r="D442" s="25" t="inlineStr">
+      <c r="D442" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -38801,7 +38819,7 @@
       <c r="G442" s="21" t="n">
         <v>2200</v>
       </c>
-      <c r="H442" s="25" t="inlineStr">
+      <c r="H442" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -38855,7 +38873,7 @@
           <t>Systems.Four_systems.ThermalOverall</t>
         </is>
       </c>
-      <c r="D443" s="18" t="inlineStr">
+      <c r="D443" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -38873,7 +38891,7 @@
       <c r="G443" s="21" t="n">
         <v>900</v>
       </c>
-      <c r="H443" s="18" t="inlineStr">
+      <c r="H443" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -38927,7 +38945,7 @@
           <t>Systems.Four_systems.ThermalOverall</t>
         </is>
       </c>
-      <c r="D444" s="25" t="inlineStr">
+      <c r="D444" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -38945,7 +38963,7 @@
       <c r="G444" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="H444" s="25" t="inlineStr">
+      <c r="H444" s="63" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -39075,7 +39093,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D446" s="25" t="inlineStr">
+      <c r="D446" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39093,7 +39111,7 @@
       <c r="G446" s="21" t="n">
         <v>0.226</v>
       </c>
-      <c r="H446" s="25" t="inlineStr">
+      <c r="H446" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39147,7 +39165,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D447" s="18" t="inlineStr">
+      <c r="D447" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39165,7 +39183,7 @@
       <c r="G447" s="21" t="n">
         <v>0.226</v>
       </c>
-      <c r="H447" s="18" t="inlineStr">
+      <c r="H447" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39219,7 +39237,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D448" s="25" t="inlineStr">
+      <c r="D448" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39237,7 +39255,7 @@
       <c r="G448" s="21" t="n">
         <v>0.34</v>
       </c>
-      <c r="H448" s="25" t="inlineStr">
+      <c r="H448" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39295,7 +39313,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D449" s="18" t="inlineStr">
+      <c r="D449" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39313,7 +39331,7 @@
       <c r="G449" s="21" t="n">
         <v>0.12</v>
       </c>
-      <c r="H449" s="18" t="inlineStr">
+      <c r="H449" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39367,7 +39385,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D450" s="25" t="inlineStr">
+      <c r="D450" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39385,7 +39403,7 @@
       <c r="G450" s="21" t="n">
         <v>-0.12</v>
       </c>
-      <c r="H450" s="25" t="inlineStr">
+      <c r="H450" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39439,7 +39457,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D451" s="18" t="inlineStr">
+      <c r="D451" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39457,7 +39475,7 @@
       <c r="G451" s="21" t="n">
         <v>0.22</v>
       </c>
-      <c r="H451" s="18" t="inlineStr">
+      <c r="H451" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39511,7 +39529,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D452" s="25" t="inlineStr">
+      <c r="D452" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39529,7 +39547,7 @@
       <c r="G452" s="21" t="n">
         <v>0.22</v>
       </c>
-      <c r="H452" s="25" t="inlineStr">
+      <c r="H452" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39583,7 +39601,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D453" s="18" t="inlineStr">
+      <c r="D453" s="62" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39601,7 +39619,7 @@
       <c r="G453" s="21" t="n">
         <v>0.012</v>
       </c>
-      <c r="H453" s="18" t="inlineStr">
+      <c r="H453" s="62" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -39655,7 +39673,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D454" s="25" t="inlineStr">
+      <c r="D454" s="63" t="inlineStr">
         <is>
           <t>Mechanical</t>
         </is>
@@ -39673,7 +39691,7 @@
       <c r="G454" s="21" t="n">
         <v>655</v>
       </c>
-      <c r="H454" s="25" t="inlineStr">
+      <c r="H454" s="63" t="inlineStr">
         <is>
           <t>kg/m³</t>
         </is>
@@ -39731,7 +39749,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D455" s="18" t="inlineStr">
+      <c r="D455" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -39749,7 +39767,7 @@
       <c r="G455" s="21" t="n">
         <v>1450</v>
       </c>
-      <c r="H455" s="18" t="inlineStr">
+      <c r="H455" s="62" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -39803,7 +39821,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D456" s="25" t="inlineStr">
+      <c r="D456" s="63" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -39821,7 +39839,7 @@
       <c r="G456" s="21" t="n">
         <v>980</v>
       </c>
-      <c r="H456" s="25" t="inlineStr">
+      <c r="H456" s="63" t="inlineStr">
         <is>
           <t>J/K</t>
         </is>
@@ -39875,7 +39893,7 @@
           <t>Components.StructureAssembly12U</t>
         </is>
       </c>
-      <c r="D457" s="18" t="inlineStr">
+      <c r="D457" s="62" t="inlineStr">
         <is>
           <t>Thermal</t>
         </is>
@@ -39893,7 +39911,7 @@
       <c r="G457" s="21" t="n">
         <v>1.6</v>
       </c>
-      <c r="H457" s="18" t="inlineStr">
+      <c r="H457" s="62" t="inlineStr">
         <is>
           <t>W/K</t>
         </is>
@@ -40108,17 +40126,17 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>Resources/Ephemeris/de440s.bsp</t>
-        </is>
-      </c>
-      <c r="C5" s="18" t="inlineStr">
+          <t>Scripts/Inputs/Ephemeris/de440s.bsp</t>
+        </is>
+      </c>
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Resources/Ephemeris/de440s.bsp</t>
+          <t>Scripts/Inputs/Ephemeris/de440s.bsp</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
@@ -40140,17 +40158,17 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>Resources/Ephemeris/finals2000A.all</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
+          <t>Scripts/Inputs/Ephemeris/finals2000A.all</t>
+        </is>
+      </c>
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>Resources/Ephemeris/finals2000A.all</t>
+          <t>Scripts/Inputs/Ephemeris/finals2000A.all</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -40172,17 +40190,17 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>Resources/Ephemeris/Leap_Second.dat</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
+          <t>Scripts/Inputs/Ephemeris/Leap_Second.dat</t>
+        </is>
+      </c>
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Resources/Ephemeris/Leap_Second.dat</t>
+          <t>Scripts/Inputs/Ephemeris/Leap_Second.dat</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -40205,7 +40223,7 @@
       <c r="B8" s="21" t="b">
         <v>1</v>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
@@ -40233,7 +40251,7 @@
       <c r="B9" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>s</t>
         </is>
@@ -40263,7 +40281,7 @@
           <t>J2SunMoon</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>text</t>
         </is>
@@ -40293,7 +40311,7 @@
       <c r="B11" s="21" t="n">
         <v>1e-10</v>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="62" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -40321,7 +40339,7 @@
       <c r="B12" s="21" t="n">
         <v>0.0001</v>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="63" t="inlineStr">
         <is>
           <t>m</t>
         </is>
